--- a/docs/research/colorado-msp-market/Colorado-MSP-Market-Research.xlsx
+++ b/docs/research/colorado-msp-market/Colorado-MSP-Market-Research.xlsx
@@ -17,8 +17,8 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Acquirers!$A$1:$I$20</definedName>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Small Shops (Roll-up)'!$A$1:$L$30</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Target List'!$A$1:$V$53</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Small Shops (Roll-up)'!$A$1:$L$34</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Target List'!$A$1:$V$56</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="959">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1320" uniqueCount="1044">
   <si>
     <t xml:space="preserve">Tier</t>
   </si>
@@ -569,7 +569,7 @@
     <t xml:space="preserve">eCreek IT Solutions</t>
   </si>
   <si>
-    <t xml:space="preserve">Greenwood Village Chamber profile: 'grown to over 22 employees in 18 years'</t>
+    <t xml:space="preserve">Greenwood Village Chamber: '22 employees in 18 years'; a separate source cites 15 — treat as 15-22</t>
   </si>
   <si>
     <t xml:space="preserve">Owner-operated / independent, self-described locally owned</t>
@@ -584,15 +584,84 @@
     <t xml:space="preserve">Targets orgs with 10-500 workstations</t>
   </si>
   <si>
-    <t xml:space="preserve">Co-managed IT, cybersecurity, compliance (HIPAA/CMMC/SOC2), VoIP; Denver/Boulder/DTC/Colo Springs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0 (1 Clutch); Inc. 5000 2025 (#3,485)</t>
+    <t xml:space="preserve">Co-managed IT, cybersecurity, compliance (HIPAA/CMMC/SOC2), VoIP; Denver/Boulder/DTC/Colo Springs/Golden/Superior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9 (80 Google); Inc. 5000 2025 (#3,485), 3 yrs running</t>
   </si>
   <si>
     <t xml:space="preserve">112% 3-yr growth per Inc. 5000</t>
   </si>
   <si>
+    <t xml:space="preserve">Office Automation Technologies, Inc. (OATI)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wheat Ridge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZoomInfo band 10-49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Independent; contact listed as David Wacker (title unconfirmed as owner)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">David Wacker (contact; ownership unverified)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31 yrs; no succession/next-gen leadership mentioned anywhere found — classic aging-owner profile by tenure alone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Managed IT, network monitoring, cybersecurity, cloud, desktop/server support; architectural/engineering/financial verticals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0 (7, Chamber)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North Star, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One aggregator says 5 (likely understated for a 30+ yr firm) — verify</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Independent, three co-owners</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Darryl Kalli, Brad Miles, Tony Quijano (co-owners, 'hands-on' ownership)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33 yrs; multi-owner structure with no stated succession plan — could signal eventual generational/exit planning need</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network support, cloud management, IT support/consulting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name collisions with other 'North Star' firms on Glassdoor/Indeed complicated verification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K3 Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greenwood Village (+ Dallas)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RocketReach/LinkedIn-derived</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Independent; owner/founder not confirmed (Jerry Kukuchka is CFO, not confirmed owner)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unknown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Young company (2017) — no retirement signal found</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Managed IT, cybersecurity, M365, practical AI automation for growing businesses; serves Golden/Brighton via location pages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~4.96 (23 Google — 22 five-star, 1 four-star)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lark IT (Lark Information Technology)</t>
   </si>
   <si>
@@ -617,9 +686,6 @@
     <t xml:space="preserve">Independent — RECLASSIFIED</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown</t>
-  </si>
-  <si>
     <t xml:space="preserve">N/A</t>
   </si>
   <si>
@@ -1466,9 +1532,6 @@
     <t xml:space="preserve">Aspire Technology Solutions</t>
   </si>
   <si>
-    <t xml:space="preserve">Wheat Ridge</t>
-  </si>
-  <si>
     <t xml:space="preserve">~11</t>
   </si>
   <si>
@@ -1928,6 +1991,108 @@
     <t xml:space="preserve">'Computer guy' consumer-facing model rather than recurring B2B managed-services book — low roll-up value despite reasonable tenure</t>
   </si>
   <si>
+    <t xml:space="preserve">SpeedWise IT Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Northglenn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-3 (BBB) — at or below size floor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECURRING — VoIP, managed IT, IT consulting, cybersecurity, cloud migration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eric Frickell (owner)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Small businesses, Northglenn/Denver metro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22-year operating history, single small owner — classic small lifestyle-business profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Very small but 22-yr locally-owned BBB A+ history is a plausible cheap tuck-in despite marginal size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BBB A+; genuine local HQ, not a satellite office</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waypoint Technology Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5-9 (ZoomInfo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help desk, network/server/cloud, cybersecurity, IT project consulting — appears B2B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not identified in this pass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colorado Front Range and beyond (unspecified)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 years operating with near-ZERO review/marketing footprint (0 reviews on Facebook and Birdeye) — inference of a steady-state, low-growth lifestyle business</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genuine local Erie HQ (rare in this pass — most 'Erie' results were satellite/national); thin marketing footprint is itself a soft signal worth a direct call</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 reviews found despite 14 yrs — verify this is not a wind-down</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITGuys (mynewitguys.com)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Denver / Lakewood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11-50 (ZoomInfo) — may exceed tuck-in range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Managed IT, on-site computer support for small businesses; notable community angle (refurbishes recycled laptops for donation)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Small businesses; serves Westminster via dedicated page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 years operating; owner unidentified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real MSP with a positive community story, but conflicting HQ claims (downtown Denver vs. Lakewood) and unidentified owner need resolving first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Workplace IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arvada / Denver (HQ conflicting across own sourcing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 (one aggregator) — very small</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Managed IT, cybersecurity, IT compliance (CMMC/ITAR/FISMA/FINRA), VoIP, cloud, structured cabling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jason Canon (per aggregator; unverified)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Front Range Fort Collins-to-Castle Rock (claimed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site claims '10+ years in Denver' which conflicts with a 2016 founding date — unresolved discrepancy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real compliance-forward service mix, but HQ location and founding date both internally inconsistent — verify directly before any outreach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7 (14 Google, per a competitor citation — secondary source)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Micro tuck-in pricing (from 2025-26 market benchmarks - see Acquirers tab):</t>
   </si>
   <si>
@@ -2660,6 +2825,27 @@
     <t xml:space="preserve">Sell-side advisor Class VI Partners (Denver); terms undisclosed</t>
   </si>
   <si>
+    <t xml:space="preserve">Mission Critical Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Westminster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11-50 employees; ~$1.8M standalone revenue (LeadIQ est., Apr 2025)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technology Architects (Minnesota-origin firm, independent merger — not PE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merger of two independent MSPs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apr 2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Combined entity now serves 4,500+ end users / 150 companies across CO/MN/WI/41 states; founder Gene Smith retained a 'continuing role' post-merger — a partial-exit succession event, not a full PE sale</t>
+  </si>
+  <si>
     <t xml:space="preserve">See the 'Acquirers' tab for the full buyer landscape, sponsors, and valuation benchmarks.</t>
   </si>
   <si>
@@ -2805,6 +2991,75 @@
   </si>
   <si>
     <t xml:space="preserve">IT staffing/recruiting firm, not an MSP, despite appearing on Clutch's Denver MSP page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BlueKey IT Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Listed as Arvada/Highlands Ranch; real HQ Mesa, AZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Runs programmatic SEO landing pages for Arvada, Thornton, Westminster, Phoenix, Scottsdale, Dallas, SLC, KC, Nashville — no evidence of a real staffed Colorado office</t>
+  </si>
+  <si>
+    <t xml:space="preserve">truit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Listed as Arvada/Boulder/Colo Springs; real HQ Tumwater/Spokane Valley, WA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Templated pages for a dozen+ CO cities; self-describes as 'nationwide', no verified CO presence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WETYR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Listed across all CO cities; likely FL-based</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not actually an MSP — a national M&amp;A/business-acquisition roll-up advisory platform with 4,400+ programmatic city x niche SEO pages across all 50 states</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NeighborTechs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Listed as Brighton/Golden/Northglenn/Lafayette; real HQ Manhasset, NY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">National chain despite 'veteran-owned' local framing; templated location pages, no real CO ops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CS Erie Computer Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Listed as Erie, CO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FALSE POSITIVE — this is Erie, PENNSYLVANIA (2005 W 8th St, Erie PA), unrelated to Erie, Colorado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colorado Technology Services LLC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Listed near Golden/Denver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Founded 2019, but actually serves Southern Colorado, not the North/West Denver metro — wrong region</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMIT Solutions of Broomfield/Erie; TeamLogic IT (Golden)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Broomfield / Erie / Golden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">National franchise chains — independently owned locations but corporate brand, not treated as independent tuck-in targets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coalfire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Large national cybersecurity advisory firm, not a small-MSP tuck-in profile</t>
   </si>
   <si>
     <t xml:space="preserve">Assumptions (edit the yellow cells - revenue estimates on 'Target List' recalculate)</t>
@@ -3649,7 +3904,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:V53"/>
+  <dimension ref="A1:V56"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -5048,7 +5303,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
         <v>160</v>
       </c>
@@ -5070,7 +5325,7 @@
         <v>22</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H21" s="9" t="n">
         <v>22</v>
@@ -5080,7 +5335,7 @@
       </c>
       <c r="J21" s="11" t="n">
         <f aca="false">IF(G21="","",ROUND(G21*Method!$B$3/1000000,1))</f>
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="K21" s="11" t="n">
         <f aca="false">IF(H21="","",ROUND(H21*Method!$B$4/1000000,1))</f>
@@ -5088,7 +5343,7 @@
       </c>
       <c r="L21" s="11" t="n">
         <f aca="false">IF(J21="","",ROUND(J21*Method!$B$6*Method!$B$7,1))</f>
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="M21" s="11" t="n">
         <f aca="false">IF(K21="","",ROUND(K21*Method!$B$6*Method!$B$8,1))</f>
@@ -5120,272 +5375,272 @@
         <v>186</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="B22" s="7" t="s">
+    <row r="22" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C22" s="8" t="str">
-        <f aca="false">HYPERLINK("https://lark-it.com","lark-it.com")</f>
-        <v>lark-it.com</v>
-      </c>
-      <c r="D22" s="7" t="s">
+      <c r="C22" s="3" t="str">
+        <f aca="false">HYPERLINK("https://oati1.com","oati1.com")</f>
+        <v>oati1.com</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>1994</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <f aca="false">IF(E22="","",Method!$B$2-E22)</f>
+        <v>32</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <f aca="false">IF(G22="","",ROUND(G22*Method!$B$3/1000000,1))</f>
+        <v>1.5</v>
+      </c>
+      <c r="K22" s="6" t="n">
+        <f aca="false">IF(H22="","",ROUND(H22*Method!$B$4/1000000,1))</f>
+        <v>9.8</v>
+      </c>
+      <c r="L22" s="6" t="n">
+        <f aca="false">IF(J22="","",ROUND(J22*Method!$B$6*Method!$B$7,1))</f>
+        <v>0.9</v>
+      </c>
+      <c r="M22" s="6" t="n">
+        <f aca="false">IF(K22="","",ROUND(K22*Method!$B$6*Method!$B$8,1))</f>
+        <v>10.3</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="P22" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="R22" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="S22" s="5"/>
+      <c r="T22" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="U22" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="V22" s="5"/>
+    </row>
+    <row r="23" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C23" s="3" t="str">
+        <f aca="false">HYPERLINK("https://www.nssit.com","www.nssit.com")</f>
+        <v>www.nssit.com</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E22" s="9" t="n">
-        <v>2003</v>
-      </c>
-      <c r="F22" s="9" t="n">
-        <f aca="false">IF(E22="","",Method!$B$2-E22)</f>
-        <v>23</v>
-      </c>
-      <c r="G22" s="9" t="n">
+      <c r="E23" s="4" t="n">
+        <v>1992</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <f aca="false">IF(E23="","",Method!$B$2-E23)</f>
+        <v>34</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H23" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="H22" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="I22" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="J22" s="11" t="n">
-        <f aca="false">IF(G22="","",ROUND(G22*Method!$B$3/1000000,1))</f>
-        <v>2.3</v>
-      </c>
-      <c r="K22" s="11" t="n">
-        <f aca="false">IF(H22="","",ROUND(H22*Method!$B$4/1000000,1))</f>
-        <v>5</v>
-      </c>
-      <c r="L22" s="11" t="n">
-        <f aca="false">IF(J22="","",ROUND(J22*Method!$B$6*Method!$B$7,1))</f>
-        <v>1.4</v>
-      </c>
-      <c r="M22" s="11" t="n">
-        <f aca="false">IF(K22="","",ROUND(K22*Method!$B$6*Method!$B$8,1))</f>
-        <v>5.3</v>
-      </c>
-      <c r="N22" s="7"/>
-      <c r="O22" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="P22" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="Q22" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="R22" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="S22" s="10"/>
-      <c r="T22" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="U22" s="7"/>
-      <c r="V22" s="10"/>
-    </row>
-    <row r="23" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="C23" s="8" t="str">
-        <f aca="false">HYPERLINK("https://springsit.com","springsit.com")</f>
-        <v>springsit.com</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="E23" s="9" t="n">
-        <v>2015</v>
-      </c>
-      <c r="F23" s="9" t="n">
-        <f aca="false">IF(E23="","",Method!$B$2-E23)</f>
-        <v>11</v>
-      </c>
-      <c r="G23" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="H23" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="I23" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="J23" s="11" t="n">
+      <c r="I23" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="J23" s="6" t="n">
         <f aca="false">IF(G23="","",ROUND(G23*Method!$B$3/1000000,1))</f>
         <v>0.8</v>
       </c>
-      <c r="K23" s="11" t="n">
+      <c r="K23" s="6" t="n">
         <f aca="false">IF(H23="","",ROUND(H23*Method!$B$4/1000000,1))</f>
         <v>3</v>
       </c>
-      <c r="L23" s="11" t="n">
+      <c r="L23" s="6" t="n">
         <f aca="false">IF(J23="","",ROUND(J23*Method!$B$6*Method!$B$7,1))</f>
         <v>0.5</v>
       </c>
-      <c r="M23" s="11" t="n">
+      <c r="M23" s="6" t="n">
         <f aca="false">IF(K23="","",ROUND(K23*Method!$B$6*Method!$B$8,1))</f>
         <v>3.2</v>
       </c>
-      <c r="N23" s="7"/>
-      <c r="O23" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="P23" s="10" t="s">
-        <v>195</v>
-      </c>
-      <c r="Q23" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="R23" s="10" t="s">
+      <c r="N23" s="2"/>
+      <c r="O23" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="S23" s="10"/>
-      <c r="T23" s="10" t="s">
+      <c r="P23" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="U23" s="7" t="s">
+      <c r="Q23" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="R23" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="V23" s="10"/>
+      <c r="S23" s="5"/>
+      <c r="T23" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="U23" s="2"/>
+      <c r="V23" s="5" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
         <v>160</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C24" s="8" t="str">
-        <f aca="false">HYPERLINK("https://rain.tech","rain.tech")</f>
-        <v>rain.tech</v>
+        <f aca="false">HYPERLINK("https://k3techs.com","k3techs.com")</f>
+        <v>k3techs.com</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>92</v>
+        <v>203</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>2001</v>
+        <v>2017</v>
       </c>
       <c r="F24" s="9" t="n">
         <f aca="false">IF(E24="","",Method!$B$2-E24)</f>
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>131</v>
+        <v>204</v>
       </c>
       <c r="J24" s="11" t="n">
         <f aca="false">IF(G24="","",ROUND(G24*Method!$B$3/1000000,1))</f>
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="K24" s="11" t="n">
         <f aca="false">IF(H24="","",ROUND(H24*Method!$B$4/1000000,1))</f>
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="L24" s="11" t="n">
         <f aca="false">IF(J24="","",ROUND(J24*Method!$B$6*Method!$B$7,1))</f>
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="M24" s="11" t="n">
         <f aca="false">IF(K24="","",ROUND(K24*Method!$B$6*Method!$B$8,1))</f>
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="N24" s="7"/>
       <c r="O24" s="10" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="P24" s="10" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="Q24" s="7" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="R24" s="10" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="S24" s="10"/>
       <c r="T24" s="10" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="U24" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="V24" s="10" t="s">
-        <v>206</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="V24" s="10"/>
     </row>
     <row r="25" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
         <v>160</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C25" s="8" t="str">
-        <f aca="false">HYPERLINK("https://coloradohitechsolutions.com","coloradohitechsolutions.com")</f>
-        <v>coloradohitechsolutions.com</v>
+        <f aca="false">HYPERLINK("https://lark-it.com","lark-it.com")</f>
+        <v>lark-it.com</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>1996</v>
+        <v>2003</v>
       </c>
       <c r="F25" s="9" t="n">
         <f aca="false">IF(E25="","",Method!$B$2-E25)</f>
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="J25" s="11" t="n">
         <f aca="false">IF(G25="","",ROUND(G25*Method!$B$3/1000000,1))</f>
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="K25" s="11" t="n">
         <f aca="false">IF(H25="","",ROUND(H25*Method!$B$4/1000000,1))</f>
-        <v>9.8</v>
+        <v>5</v>
       </c>
       <c r="L25" s="11" t="n">
         <f aca="false">IF(J25="","",ROUND(J25*Method!$B$6*Method!$B$7,1))</f>
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="M25" s="11" t="n">
         <f aca="false">IF(K25="","",ROUND(K25*Method!$B$6*Method!$B$8,1))</f>
-        <v>10.3</v>
+        <v>5.3</v>
       </c>
       <c r="N25" s="7"/>
       <c r="O25" s="10" t="s">
-        <v>209</v>
+        <v>61</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q25" s="7" t="s">
         <v>45</v>
       </c>
       <c r="R25" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="S25" s="10"/>
       <c r="T25" s="10" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="U25" s="7"/>
       <c r="V25" s="10"/>
@@ -5395,30 +5650,30 @@
         <v>160</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C26" s="8" t="str">
-        <f aca="false">HYPERLINK("https://techframework.com","techframework.com")</f>
-        <v>techframework.com</v>
+        <f aca="false">HYPERLINK("https://springsit.com","springsit.com")</f>
+        <v>springsit.com</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>214</v>
+        <v>92</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>2012</v>
+        <v>2015</v>
       </c>
       <c r="F26" s="9" t="n">
         <f aca="false">IF(E26="","",Method!$B$2-E26)</f>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G26" s="9" t="n">
         <v>5</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J26" s="11" t="n">
         <f aca="false">IF(G26="","",ROUND(G26*Method!$B$3/1000000,1))</f>
@@ -5426,7 +5681,7 @@
       </c>
       <c r="K26" s="11" t="n">
         <f aca="false">IF(H26="","",ROUND(H26*Method!$B$4/1000000,1))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L26" s="11" t="n">
         <f aca="false">IF(J26="","",ROUND(J26*Method!$B$6*Method!$B$7,1))</f>
@@ -5434,61 +5689,59 @@
       </c>
       <c r="M26" s="11" t="n">
         <f aca="false">IF(K26="","",ROUND(K26*Method!$B$6*Method!$B$8,1))</f>
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="N26" s="7"/>
       <c r="O26" s="10" t="s">
-        <v>36</v>
+        <v>217</v>
       </c>
       <c r="P26" s="10" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="Q26" s="7" t="s">
-        <v>125</v>
+        <v>218</v>
       </c>
       <c r="R26" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="S26" s="10" t="s">
-        <v>218</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="S26" s="10"/>
       <c r="T26" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="U26" s="7"/>
-      <c r="V26" s="10" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="U26" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="V26" s="10"/>
+    </row>
+    <row r="27" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
         <v>160</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C27" s="8" t="str">
-        <f aca="false">HYPERLINK("https://ipoint-tech.com","ipoint-tech.com")</f>
-        <v>ipoint-tech.com</v>
+        <f aca="false">HYPERLINK("https://rain.tech","rain.tech")</f>
+        <v>rain.tech</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>24</v>
+        <v>92</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="F27" s="9" t="n">
         <f aca="false">IF(E27="","",Method!$B$2-E27)</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G27" s="9" t="n">
         <v>10</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>222</v>
+        <v>131</v>
       </c>
       <c r="J27" s="11" t="n">
         <f aca="false">IF(G27="","",ROUND(G27*Method!$B$3/1000000,1))</f>
@@ -5496,7 +5749,7 @@
       </c>
       <c r="K27" s="11" t="n">
         <f aca="false">IF(H27="","",ROUND(H27*Method!$B$4/1000000,1))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L27" s="11" t="n">
         <f aca="false">IF(J27="","",ROUND(J27*Method!$B$6*Method!$B$7,1))</f>
@@ -5504,19 +5757,17 @@
       </c>
       <c r="M27" s="11" t="n">
         <f aca="false">IF(K27="","",ROUND(K27*Method!$B$6*Method!$B$8,1))</f>
-        <v>4.2</v>
-      </c>
-      <c r="N27" s="7" t="s">
+        <v>5.3</v>
+      </c>
+      <c r="N27" s="7"/>
+      <c r="O27" s="10" t="s">
         <v>223</v>
-      </c>
-      <c r="O27" s="10" t="s">
-        <v>36</v>
       </c>
       <c r="P27" s="10" t="s">
         <v>224</v>
       </c>
       <c r="Q27" s="7" t="s">
-        <v>45</v>
+        <v>148</v>
       </c>
       <c r="R27" s="10" t="s">
         <v>225</v>
@@ -5525,71 +5776,75 @@
       <c r="T27" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="U27" s="7"/>
-      <c r="V27" s="10"/>
-    </row>
-    <row r="28" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="U27" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="V27" s="10" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
         <v>160</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C28" s="8" t="str">
-        <f aca="false">HYPERLINK("https://crownpointsolutions.com","crownpointsolutions.com")</f>
-        <v>crownpointsolutions.com</v>
+        <f aca="false">HYPERLINK("https://coloradohitechsolutions.com","coloradohitechsolutions.com")</f>
+        <v>coloradohitechsolutions.com</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>228</v>
+        <v>92</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>2003</v>
+        <v>1996</v>
       </c>
       <c r="F28" s="9" t="n">
         <f aca="false">IF(E28="","",Method!$B$2-E28)</f>
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>193</v>
+        <v>230</v>
       </c>
       <c r="J28" s="11" t="n">
         <f aca="false">IF(G28="","",ROUND(G28*Method!$B$3/1000000,1))</f>
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="K28" s="11" t="n">
         <f aca="false">IF(H28="","",ROUND(H28*Method!$B$4/1000000,1))</f>
-        <v>3</v>
+        <v>9.8</v>
       </c>
       <c r="L28" s="11" t="n">
         <f aca="false">IF(J28="","",ROUND(J28*Method!$B$6*Method!$B$7,1))</f>
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="M28" s="11" t="n">
         <f aca="false">IF(K28="","",ROUND(K28*Method!$B$6*Method!$B$8,1))</f>
-        <v>3.2</v>
+        <v>10.3</v>
       </c>
       <c r="N28" s="7"/>
       <c r="O28" s="10" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="P28" s="10" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q28" s="7" t="s">
-        <v>148</v>
+        <v>45</v>
       </c>
       <c r="R28" s="10" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="S28" s="10"/>
       <c r="T28" s="10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="U28" s="7"/>
       <c r="V28" s="10"/>
@@ -5599,52 +5854,50 @@
         <v>160</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C29" s="8" t="str">
-        <f aca="false">HYPERLINK("https://www.cpcolorado.com","www.cpcolorado.com")</f>
-        <v>www.cpcolorado.com</v>
+        <f aca="false">HYPERLINK("https://techframework.com","techframework.com")</f>
+        <v>techframework.com</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>1985</v>
+        <v>2012</v>
       </c>
       <c r="F29" s="9" t="n">
         <f aca="false">IF(E29="","",Method!$B$2-E29)</f>
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="J29" s="11" t="n">
         <f aca="false">IF(G29="","",ROUND(G29*Method!$B$3/1000000,1))</f>
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="K29" s="11" t="n">
         <f aca="false">IF(H29="","",ROUND(H29*Method!$B$4/1000000,1))</f>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L29" s="11" t="n">
         <f aca="false">IF(J29="","",ROUND(J29*Method!$B$6*Method!$B$7,1))</f>
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="M29" s="11" t="n">
         <f aca="false">IF(K29="","",ROUND(K29*Method!$B$6*Method!$B$8,1))</f>
-        <v>6.3</v>
-      </c>
-      <c r="N29" s="7" t="s">
-        <v>236</v>
-      </c>
+        <v>2.1</v>
+      </c>
+      <c r="N29" s="7"/>
       <c r="O29" s="10" t="s">
-        <v>237</v>
+        <v>36</v>
       </c>
       <c r="P29" s="10" t="s">
         <v>238</v>
@@ -5655,18 +5908,18 @@
       <c r="R29" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="S29" s="10"/>
+      <c r="S29" s="10" t="s">
+        <v>240</v>
+      </c>
       <c r="T29" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="U29" s="7" t="s">
         <v>241</v>
       </c>
+      <c r="U29" s="7"/>
       <c r="V29" s="10" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
         <v>160</v>
       </c>
@@ -5674,42 +5927,49 @@
         <v>243</v>
       </c>
       <c r="C30" s="8" t="str">
-        <f aca="false">HYPERLINK("https://windwardnetworks.com","windwardnetworks.com")</f>
-        <v>windwardnetworks.com</v>
+        <f aca="false">HYPERLINK("https://ipoint-tech.com","ipoint-tech.com")</f>
+        <v>ipoint-tech.com</v>
       </c>
       <c r="D30" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>2002</v>
+      </c>
+      <c r="F30" s="9" t="n">
+        <f aca="false">IF(E30="","",Method!$B$2-E30)</f>
+        <v>24</v>
+      </c>
+      <c r="G30" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="H30" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="I30" s="10" t="s">
         <v>244</v>
-      </c>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="H30" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="I30" s="10" t="s">
-        <v>131</v>
       </c>
       <c r="J30" s="11" t="n">
         <f aca="false">IF(G30="","",ROUND(G30*Method!$B$3/1000000,1))</f>
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="K30" s="11" t="n">
         <f aca="false">IF(H30="","",ROUND(H30*Method!$B$4/1000000,1))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L30" s="11" t="n">
         <f aca="false">IF(J30="","",ROUND(J30*Method!$B$6*Method!$B$7,1))</f>
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="M30" s="11" t="n">
         <f aca="false">IF(K30="","",ROUND(K30*Method!$B$6*Method!$B$8,1))</f>
-        <v>3.2</v>
-      </c>
-      <c r="N30" s="7"/>
+        <v>4.2</v>
+      </c>
+      <c r="N30" s="7" t="s">
+        <v>245</v>
+      </c>
       <c r="O30" s="10" t="s">
-        <v>245</v>
+        <v>36</v>
       </c>
       <c r="P30" s="10" t="s">
         <v>246</v>
@@ -5727,367 +5987,370 @@
       <c r="U30" s="7"/>
       <c r="V30" s="10"/>
     </row>
-    <row r="31" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="B31" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="C31" s="8" t="str">
+        <f aca="false">HYPERLINK("https://crownpointsolutions.com","crownpointsolutions.com")</f>
+        <v>crownpointsolutions.com</v>
+      </c>
+      <c r="D31" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="C31" s="8" t="str">
-        <f aca="false">HYPERLINK("https://simpinc.com","simpinc.com")</f>
-        <v>simpinc.com</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>251</v>
-      </c>
       <c r="E31" s="9" t="n">
-        <v>1993</v>
+        <v>2003</v>
       </c>
       <c r="F31" s="9" t="n">
         <f aca="false">IF(E31="","",Method!$B$2-E31)</f>
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>252</v>
+        <v>216</v>
       </c>
       <c r="J31" s="11" t="n">
         <f aca="false">IF(G31="","",ROUND(G31*Method!$B$3/1000000,1))</f>
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="K31" s="11" t="n">
         <f aca="false">IF(H31="","",ROUND(H31*Method!$B$4/1000000,1))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L31" s="11" t="n">
         <f aca="false">IF(J31="","",ROUND(J31*Method!$B$6*Method!$B$7,1))</f>
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="M31" s="11" t="n">
         <f aca="false">IF(K31="","",ROUND(K31*Method!$B$6*Method!$B$8,1))</f>
-        <v>5.3</v>
+        <v>3.2</v>
       </c>
       <c r="N31" s="7"/>
       <c r="O31" s="10" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="Q31" s="7" t="s">
         <v>148</v>
       </c>
       <c r="R31" s="10" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="S31" s="10"/>
       <c r="T31" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="U31" s="7"/>
+      <c r="V31" s="10"/>
+    </row>
+    <row r="32" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="C32" s="8" t="str">
+        <f aca="false">HYPERLINK("https://www.cpcolorado.com","www.cpcolorado.com")</f>
+        <v>www.cpcolorado.com</v>
+      </c>
+      <c r="D32" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="U31" s="7"/>
-      <c r="V31" s="10" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="C32" s="8" t="str">
-        <f aca="false">HYPERLINK("https://www.trutechit.com","www.trutechit.com")</f>
-        <v>www.trutechit.com</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>259</v>
-      </c>
       <c r="E32" s="9" t="n">
-        <v>2010</v>
+        <v>1985</v>
       </c>
       <c r="F32" s="9" t="n">
         <f aca="false">IF(E32="","",Method!$B$2-E32)</f>
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>193</v>
+        <v>257</v>
       </c>
       <c r="J32" s="11" t="n">
         <f aca="false">IF(G32="","",ROUND(G32*Method!$B$3/1000000,1))</f>
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="K32" s="11" t="n">
         <f aca="false">IF(H32="","",ROUND(H32*Method!$B$4/1000000,1))</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L32" s="11" t="n">
         <f aca="false">IF(J32="","",ROUND(J32*Method!$B$6*Method!$B$7,1))</f>
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="M32" s="11" t="n">
         <f aca="false">IF(K32="","",ROUND(K32*Method!$B$6*Method!$B$8,1))</f>
-        <v>4.2</v>
-      </c>
-      <c r="N32" s="7"/>
+        <v>6.3</v>
+      </c>
+      <c r="N32" s="7" t="s">
+        <v>258</v>
+      </c>
       <c r="O32" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="P32" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="P32" s="10" t="s">
+      <c r="Q32" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="R32" s="10" t="s">
         <v>261</v>
-      </c>
-      <c r="Q32" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="R32" s="10" t="s">
-        <v>203</v>
       </c>
       <c r="S32" s="10"/>
       <c r="T32" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="U32" s="7"/>
+      <c r="U32" s="7" t="s">
+        <v>263</v>
+      </c>
       <c r="V32" s="10" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>249</v>
+        <v>160</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C33" s="8" t="str">
+        <f aca="false">HYPERLINK("https://windwardnetworks.com","windwardnetworks.com")</f>
+        <v>windwardnetworks.com</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H33" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="I33" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="J33" s="11" t="n">
+        <f aca="false">IF(G33="","",ROUND(G33*Method!$B$3/1000000,1))</f>
+        <v>0.8</v>
+      </c>
+      <c r="K33" s="11" t="n">
+        <f aca="false">IF(H33="","",ROUND(H33*Method!$B$4/1000000,1))</f>
+        <v>3</v>
+      </c>
+      <c r="L33" s="11" t="n">
+        <f aca="false">IF(J33="","",ROUND(J33*Method!$B$6*Method!$B$7,1))</f>
+        <v>0.5</v>
+      </c>
+      <c r="M33" s="11" t="n">
+        <f aca="false">IF(K33="","",ROUND(K33*Method!$B$6*Method!$B$8,1))</f>
+        <v>3.2</v>
+      </c>
+      <c r="N33" s="7"/>
+      <c r="O33" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="P33" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q33" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="R33" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="S33" s="10"/>
+      <c r="T33" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="U33" s="7"/>
+      <c r="V33" s="10"/>
+    </row>
+    <row r="34" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="C34" s="8" t="str">
+        <f aca="false">HYPERLINK("https://simpinc.com","simpinc.com")</f>
+        <v>simpinc.com</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>1993</v>
+      </c>
+      <c r="F34" s="9" t="n">
+        <f aca="false">IF(E34="","",Method!$B$2-E34)</f>
+        <v>33</v>
+      </c>
+      <c r="G34" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="H34" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="I34" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="J34" s="11" t="n">
+        <f aca="false">IF(G34="","",ROUND(G34*Method!$B$3/1000000,1))</f>
+        <v>1.5</v>
+      </c>
+      <c r="K34" s="11" t="n">
+        <f aca="false">IF(H34="","",ROUND(H34*Method!$B$4/1000000,1))</f>
+        <v>5</v>
+      </c>
+      <c r="L34" s="11" t="n">
+        <f aca="false">IF(J34="","",ROUND(J34*Method!$B$6*Method!$B$7,1))</f>
+        <v>0.9</v>
+      </c>
+      <c r="M34" s="11" t="n">
+        <f aca="false">IF(K34="","",ROUND(K34*Method!$B$6*Method!$B$8,1))</f>
+        <v>5.3</v>
+      </c>
+      <c r="N34" s="7"/>
+      <c r="O34" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="P34" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="Q34" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="R34" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="S34" s="10"/>
+      <c r="T34" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="U34" s="7"/>
+      <c r="V34" s="10" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="C35" s="8" t="str">
+        <f aca="false">HYPERLINK("https://www.trutechit.com","www.trutechit.com")</f>
+        <v>www.trutechit.com</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>2010</v>
+      </c>
+      <c r="F35" s="9" t="n">
+        <f aca="false">IF(E35="","",Method!$B$2-E35)</f>
+        <v>16</v>
+      </c>
+      <c r="G35" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="H35" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="I35" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="J35" s="11" t="n">
+        <f aca="false">IF(G35="","",ROUND(G35*Method!$B$3/1000000,1))</f>
+        <v>1.5</v>
+      </c>
+      <c r="K35" s="11" t="n">
+        <f aca="false">IF(H35="","",ROUND(H35*Method!$B$4/1000000,1))</f>
+        <v>4</v>
+      </c>
+      <c r="L35" s="11" t="n">
+        <f aca="false">IF(J35="","",ROUND(J35*Method!$B$6*Method!$B$7,1))</f>
+        <v>0.9</v>
+      </c>
+      <c r="M35" s="11" t="n">
+        <f aca="false">IF(K35="","",ROUND(K35*Method!$B$6*Method!$B$8,1))</f>
+        <v>4.2</v>
+      </c>
+      <c r="N35" s="7"/>
+      <c r="O35" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="P35" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q35" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="R35" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="S35" s="10"/>
+      <c r="T35" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="U35" s="7"/>
+      <c r="V35" s="10" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="C36" s="8" t="str">
         <f aca="false">HYPERLINK("https://steppingforward.tech","steppingforward.tech")</f>
         <v>steppingforward.tech</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D36" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="E33" s="9" t="n">
+      <c r="E36" s="9" t="n">
         <v>2006</v>
-      </c>
-      <c r="F33" s="9" t="n">
-        <f aca="false">IF(E33="","",Method!$B$2-E33)</f>
-        <v>20</v>
-      </c>
-      <c r="G33" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="H33" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="I33" s="10" t="s">
-        <v>265</v>
-      </c>
-      <c r="J33" s="11" t="n">
-        <f aca="false">IF(G33="","",ROUND(G33*Method!$B$3/1000000,1))</f>
-        <v>1.5</v>
-      </c>
-      <c r="K33" s="11" t="n">
-        <f aca="false">IF(H33="","",ROUND(H33*Method!$B$4/1000000,1))</f>
-        <v>2.4</v>
-      </c>
-      <c r="L33" s="11" t="n">
-        <f aca="false">IF(J33="","",ROUND(J33*Method!$B$6*Method!$B$7,1))</f>
-        <v>0.9</v>
-      </c>
-      <c r="M33" s="11" t="n">
-        <f aca="false">IF(K33="","",ROUND(K33*Method!$B$6*Method!$B$8,1))</f>
-        <v>2.5</v>
-      </c>
-      <c r="N33" s="7"/>
-      <c r="O33" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="P33" s="10" t="s">
-        <v>267</v>
-      </c>
-      <c r="Q33" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="R33" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="S33" s="10"/>
-      <c r="T33" s="10" t="s">
-        <v>268</v>
-      </c>
-      <c r="U33" s="7"/>
-      <c r="V33" s="10"/>
-    </row>
-    <row r="34" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="E34" s="9" t="n">
-        <v>2003</v>
-      </c>
-      <c r="F34" s="9" t="n">
-        <f aca="false">IF(E34="","",Method!$B$2-E34)</f>
-        <v>23</v>
-      </c>
-      <c r="G34" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="H34" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="I34" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="J34" s="11" t="n">
-        <f aca="false">IF(G34="","",ROUND(G34*Method!$B$3/1000000,1))</f>
-        <v>0.8</v>
-      </c>
-      <c r="K34" s="11" t="n">
-        <f aca="false">IF(H34="","",ROUND(H34*Method!$B$4/1000000,1))</f>
-        <v>3</v>
-      </c>
-      <c r="L34" s="11" t="n">
-        <f aca="false">IF(J34="","",ROUND(J34*Method!$B$6*Method!$B$7,1))</f>
-        <v>0.5</v>
-      </c>
-      <c r="M34" s="11" t="n">
-        <f aca="false">IF(K34="","",ROUND(K34*Method!$B$6*Method!$B$8,1))</f>
-        <v>3.2</v>
-      </c>
-      <c r="N34" s="7"/>
-      <c r="O34" s="10" t="s">
-        <v>271</v>
-      </c>
-      <c r="P34" s="10" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q34" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="R34" s="10" t="s">
-        <v>272</v>
-      </c>
-      <c r="S34" s="10"/>
-      <c r="T34" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="U34" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="V34" s="10" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="C35" s="8" t="str">
-        <f aca="false">HYPERLINK("https://www.trioptech.com","www.trioptech.com")</f>
-        <v>www.trioptech.com</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="H35" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="I35" s="10" t="s">
-        <v>278</v>
-      </c>
-      <c r="J35" s="11" t="n">
-        <f aca="false">IF(G35="","",ROUND(G35*Method!$B$3/1000000,1))</f>
-        <v>0.5</v>
-      </c>
-      <c r="K35" s="11" t="n">
-        <f aca="false">IF(H35="","",ROUND(H35*Method!$B$4/1000000,1))</f>
-        <v>1</v>
-      </c>
-      <c r="L35" s="11" t="n">
-        <f aca="false">IF(J35="","",ROUND(J35*Method!$B$6*Method!$B$7,1))</f>
-        <v>0.3</v>
-      </c>
-      <c r="M35" s="11" t="n">
-        <f aca="false">IF(K35="","",ROUND(K35*Method!$B$6*Method!$B$8,1))</f>
-        <v>1.1</v>
-      </c>
-      <c r="N35" s="7"/>
-      <c r="O35" s="10" t="s">
-        <v>261</v>
-      </c>
-      <c r="P35" s="10" t="s">
-        <v>279</v>
-      </c>
-      <c r="Q35" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="R35" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="S35" s="10"/>
-      <c r="T35" s="10" t="s">
-        <v>280</v>
-      </c>
-      <c r="U35" s="7"/>
-      <c r="V35" s="10" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>282</v>
-      </c>
-      <c r="C36" s="8" t="str">
-        <f aca="false">HYPERLINK("https://www.koshsolutions.com","www.koshsolutions.com")</f>
-        <v>www.koshsolutions.com</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="E36" s="9" t="n">
-        <v>2005</v>
       </c>
       <c r="F36" s="9" t="n">
         <f aca="false">IF(E36="","",Method!$B$2-E36)</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G36" s="9" t="n">
         <v>10</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="J36" s="11" t="n">
         <f aca="false">IF(G36="","",ROUND(G36*Method!$B$3/1000000,1))</f>
@@ -6095,7 +6358,7 @@
       </c>
       <c r="K36" s="11" t="n">
         <f aca="false">IF(H36="","",ROUND(H36*Method!$B$4/1000000,1))</f>
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="L36" s="11" t="n">
         <f aca="false">IF(J36="","",ROUND(J36*Method!$B$6*Method!$B$7,1))</f>
@@ -6103,415 +6366,409 @@
       </c>
       <c r="M36" s="11" t="n">
         <f aca="false">IF(K36="","",ROUND(K36*Method!$B$6*Method!$B$8,1))</f>
-        <v>5.3</v>
+        <v>2.5</v>
       </c>
       <c r="N36" s="7"/>
       <c r="O36" s="10" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="P36" s="10" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q36" s="7" t="s">
         <v>148</v>
       </c>
       <c r="R36" s="10" t="s">
-        <v>287</v>
+        <v>225</v>
       </c>
       <c r="S36" s="10"/>
       <c r="T36" s="10" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="U36" s="7"/>
-      <c r="V36" s="10" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="12" t="s">
-        <v>290</v>
-      </c>
-      <c r="B37" s="12" t="s">
+      <c r="V36" s="10"/>
+    </row>
+    <row r="37" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="B37" s="7" t="s">
         <v>291</v>
       </c>
-      <c r="C37" s="13" t="str">
+      <c r="C37" s="7"/>
+      <c r="D37" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>2003</v>
+      </c>
+      <c r="F37" s="9" t="n">
+        <f aca="false">IF(E37="","",Method!$B$2-E37)</f>
+        <v>23</v>
+      </c>
+      <c r="G37" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H37" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="I37" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="J37" s="11" t="n">
+        <f aca="false">IF(G37="","",ROUND(G37*Method!$B$3/1000000,1))</f>
+        <v>0.8</v>
+      </c>
+      <c r="K37" s="11" t="n">
+        <f aca="false">IF(H37="","",ROUND(H37*Method!$B$4/1000000,1))</f>
+        <v>3</v>
+      </c>
+      <c r="L37" s="11" t="n">
+        <f aca="false">IF(J37="","",ROUND(J37*Method!$B$6*Method!$B$7,1))</f>
+        <v>0.5</v>
+      </c>
+      <c r="M37" s="11" t="n">
+        <f aca="false">IF(K37="","",ROUND(K37*Method!$B$6*Method!$B$8,1))</f>
+        <v>3.2</v>
+      </c>
+      <c r="N37" s="7"/>
+      <c r="O37" s="10" t="s">
+        <v>293</v>
+      </c>
+      <c r="P37" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q37" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="R37" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="S37" s="10"/>
+      <c r="T37" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="U37" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="V37" s="10" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="C38" s="8" t="str">
+        <f aca="false">HYPERLINK("https://www.trioptech.com","www.trioptech.com")</f>
+        <v>www.trioptech.com</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H38" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I38" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="J38" s="11" t="n">
+        <f aca="false">IF(G38="","",ROUND(G38*Method!$B$3/1000000,1))</f>
+        <v>0.5</v>
+      </c>
+      <c r="K38" s="11" t="n">
+        <f aca="false">IF(H38="","",ROUND(H38*Method!$B$4/1000000,1))</f>
+        <v>1</v>
+      </c>
+      <c r="L38" s="11" t="n">
+        <f aca="false">IF(J38="","",ROUND(J38*Method!$B$6*Method!$B$7,1))</f>
+        <v>0.3</v>
+      </c>
+      <c r="M38" s="11" t="n">
+        <f aca="false">IF(K38="","",ROUND(K38*Method!$B$6*Method!$B$8,1))</f>
+        <v>1.1</v>
+      </c>
+      <c r="N38" s="7"/>
+      <c r="O38" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="P38" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="Q38" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="R38" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="S38" s="10"/>
+      <c r="T38" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="U38" s="7"/>
+      <c r="V38" s="10" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="C39" s="8" t="str">
+        <f aca="false">HYPERLINK("https://www.koshsolutions.com","www.koshsolutions.com")</f>
+        <v>www.koshsolutions.com</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>2005</v>
+      </c>
+      <c r="F39" s="9" t="n">
+        <f aca="false">IF(E39="","",Method!$B$2-E39)</f>
+        <v>21</v>
+      </c>
+      <c r="G39" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="H39" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="I39" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="J39" s="11" t="n">
+        <f aca="false">IF(G39="","",ROUND(G39*Method!$B$3/1000000,1))</f>
+        <v>1.5</v>
+      </c>
+      <c r="K39" s="11" t="n">
+        <f aca="false">IF(H39="","",ROUND(H39*Method!$B$4/1000000,1))</f>
+        <v>5</v>
+      </c>
+      <c r="L39" s="11" t="n">
+        <f aca="false">IF(J39="","",ROUND(J39*Method!$B$6*Method!$B$7,1))</f>
+        <v>0.9</v>
+      </c>
+      <c r="M39" s="11" t="n">
+        <f aca="false">IF(K39="","",ROUND(K39*Method!$B$6*Method!$B$8,1))</f>
+        <v>5.3</v>
+      </c>
+      <c r="N39" s="7"/>
+      <c r="O39" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="P39" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="Q39" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="R39" s="10" t="s">
+        <v>309</v>
+      </c>
+      <c r="S39" s="10"/>
+      <c r="T39" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="U39" s="7"/>
+      <c r="V39" s="10" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="C40" s="13" t="str">
         <f aca="false">HYPERLINK("https://www.nexustek.com","www.nexustek.com")</f>
         <v>www.nexustek.com</v>
       </c>
-      <c r="D37" s="12" t="s">
-        <v>292</v>
-      </c>
-      <c r="E37" s="14" t="n">
+      <c r="D40" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="E40" s="14" t="n">
         <v>1996</v>
       </c>
-      <c r="F37" s="14" t="n">
-        <f aca="false">IF(E37="","",Method!$B$2-E37)</f>
+      <c r="F40" s="14" t="n">
+        <f aca="false">IF(E40="","",Method!$B$2-E40)</f>
         <v>30</v>
       </c>
-      <c r="G37" s="14" t="n">
+      <c r="G40" s="14" t="n">
         <v>250</v>
       </c>
-      <c r="H37" s="14" t="n">
+      <c r="H40" s="14" t="n">
         <v>750</v>
       </c>
-      <c r="I37" s="15" t="s">
-        <v>293</v>
-      </c>
-      <c r="J37" s="16" t="n">
-        <f aca="false">IF(G37="","",ROUND(G37*Method!$B$3/1000000,1))</f>
+      <c r="I40" s="15" t="s">
+        <v>315</v>
+      </c>
+      <c r="J40" s="16" t="n">
+        <f aca="false">IF(G40="","",ROUND(G40*Method!$B$3/1000000,1))</f>
         <v>37.5</v>
       </c>
-      <c r="K37" s="16" t="n">
-        <f aca="false">IF(H37="","",ROUND(H37*Method!$B$4/1000000,1))</f>
+      <c r="K40" s="16" t="n">
+        <f aca="false">IF(H40="","",ROUND(H40*Method!$B$4/1000000,1))</f>
         <v>150</v>
       </c>
-      <c r="L37" s="16" t="n">
-        <f aca="false">IF(J37="","",ROUND(J37*Method!$B$6*Method!$B$7,1))</f>
+      <c r="L40" s="16" t="n">
+        <f aca="false">IF(J40="","",ROUND(J40*Method!$B$6*Method!$B$7,1))</f>
         <v>22.5</v>
       </c>
-      <c r="M37" s="16" t="n">
-        <f aca="false">IF(K37="","",ROUND(K37*Method!$B$6*Method!$B$8,1))</f>
+      <c r="M40" s="16" t="n">
+        <f aca="false">IF(K40="","",ROUND(K40*Method!$B$6*Method!$B$8,1))</f>
         <v>157.5</v>
       </c>
-      <c r="N37" s="12"/>
-      <c r="O37" s="15" t="s">
-        <v>294</v>
-      </c>
-      <c r="P37" s="15" t="s">
-        <v>295</v>
-      </c>
-      <c r="Q37" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="R37" s="15" t="s">
-        <v>296</v>
-      </c>
-      <c r="S37" s="15"/>
-      <c r="T37" s="15" t="s">
-        <v>297</v>
-      </c>
-      <c r="U37" s="12" t="s">
-        <v>298</v>
-      </c>
-      <c r="V37" s="15" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="12" t="s">
-        <v>290</v>
-      </c>
-      <c r="B38" s="12" t="s">
-        <v>300</v>
-      </c>
-      <c r="C38" s="13" t="str">
+      <c r="N40" s="12"/>
+      <c r="O40" s="15" t="s">
+        <v>316</v>
+      </c>
+      <c r="P40" s="15" t="s">
+        <v>317</v>
+      </c>
+      <c r="Q40" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="R40" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="S40" s="15"/>
+      <c r="T40" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="U40" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="V40" s="15" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="C41" s="13" t="str">
         <f aca="false">HYPERLINK("https://www.greystonetech.com","www.greystonetech.com")</f>
         <v>www.greystonetech.com</v>
       </c>
-      <c r="D38" s="12" t="s">
-        <v>301</v>
-      </c>
-      <c r="E38" s="14" t="n">
+      <c r="D41" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="E41" s="14" t="n">
         <v>2001</v>
       </c>
-      <c r="F38" s="14" t="n">
-        <f aca="false">IF(E38="","",Method!$B$2-E38)</f>
+      <c r="F41" s="14" t="n">
+        <f aca="false">IF(E41="","",Method!$B$2-E41)</f>
         <v>25</v>
       </c>
-      <c r="G38" s="14" t="n">
+      <c r="G41" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="H38" s="14" t="n">
+      <c r="H41" s="14" t="n">
         <v>249</v>
       </c>
-      <c r="I38" s="15" t="s">
-        <v>302</v>
-      </c>
-      <c r="J38" s="16" t="n">
-        <f aca="false">IF(G38="","",ROUND(G38*Method!$B$3/1000000,1))</f>
+      <c r="I41" s="15" t="s">
+        <v>324</v>
+      </c>
+      <c r="J41" s="16" t="n">
+        <f aca="false">IF(G41="","",ROUND(G41*Method!$B$3/1000000,1))</f>
         <v>15</v>
       </c>
-      <c r="K38" s="16" t="n">
-        <f aca="false">IF(H38="","",ROUND(H38*Method!$B$4/1000000,1))</f>
+      <c r="K41" s="16" t="n">
+        <f aca="false">IF(H41="","",ROUND(H41*Method!$B$4/1000000,1))</f>
         <v>49.8</v>
       </c>
-      <c r="L38" s="16" t="n">
-        <f aca="false">IF(J38="","",ROUND(J38*Method!$B$6*Method!$B$7,1))</f>
+      <c r="L41" s="16" t="n">
+        <f aca="false">IF(J41="","",ROUND(J41*Method!$B$6*Method!$B$7,1))</f>
         <v>9</v>
       </c>
-      <c r="M38" s="16" t="n">
-        <f aca="false">IF(K38="","",ROUND(K38*Method!$B$6*Method!$B$8,1))</f>
+      <c r="M41" s="16" t="n">
+        <f aca="false">IF(K41="","",ROUND(K41*Method!$B$6*Method!$B$8,1))</f>
         <v>52.3</v>
       </c>
-      <c r="N38" s="12"/>
-      <c r="O38" s="15" t="s">
-        <v>303</v>
-      </c>
-      <c r="P38" s="15" t="s">
-        <v>304</v>
-      </c>
-      <c r="Q38" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="R38" s="15" t="s">
-        <v>305</v>
-      </c>
-      <c r="S38" s="15"/>
-      <c r="T38" s="15" t="s">
-        <v>306</v>
-      </c>
-      <c r="U38" s="12"/>
-      <c r="V38" s="15" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="12" t="s">
-        <v>290</v>
-      </c>
-      <c r="B39" s="12" t="s">
-        <v>308</v>
-      </c>
-      <c r="C39" s="13" t="str">
+      <c r="N41" s="12"/>
+      <c r="O41" s="15" t="s">
+        <v>325</v>
+      </c>
+      <c r="P41" s="15" t="s">
+        <v>326</v>
+      </c>
+      <c r="Q41" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="R41" s="15" t="s">
+        <v>327</v>
+      </c>
+      <c r="S41" s="15"/>
+      <c r="T41" s="15" t="s">
+        <v>328</v>
+      </c>
+      <c r="U41" s="12"/>
+      <c r="V41" s="15" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>330</v>
+      </c>
+      <c r="C42" s="13" t="str">
         <f aca="false">HYPERLINK("https://harborit.com","harborit.com")</f>
         <v>harborit.com</v>
       </c>
-      <c r="D39" s="12" t="s">
+      <c r="D42" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="E39" s="14" t="n">
+      <c r="E42" s="14" t="n">
         <v>2006</v>
-      </c>
-      <c r="F39" s="14" t="n">
-        <f aca="false">IF(E39="","",Method!$B$2-E39)</f>
-        <v>20</v>
-      </c>
-      <c r="G39" s="14" t="n">
-        <v>375</v>
-      </c>
-      <c r="H39" s="14" t="n">
-        <v>375</v>
-      </c>
-      <c r="I39" s="15" t="s">
-        <v>309</v>
-      </c>
-      <c r="J39" s="16" t="n">
-        <f aca="false">IF(G39="","",ROUND(G39*Method!$B$3/1000000,1))</f>
-        <v>56.3</v>
-      </c>
-      <c r="K39" s="16" t="n">
-        <f aca="false">IF(H39="","",ROUND(H39*Method!$B$4/1000000,1))</f>
-        <v>75</v>
-      </c>
-      <c r="L39" s="16" t="n">
-        <f aca="false">IF(J39="","",ROUND(J39*Method!$B$6*Method!$B$7,1))</f>
-        <v>33.8</v>
-      </c>
-      <c r="M39" s="16" t="n">
-        <f aca="false">IF(K39="","",ROUND(K39*Method!$B$6*Method!$B$8,1))</f>
-        <v>78.8</v>
-      </c>
-      <c r="N39" s="12"/>
-      <c r="O39" s="15" t="s">
-        <v>310</v>
-      </c>
-      <c r="P39" s="15" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q39" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="R39" s="15" t="s">
-        <v>312</v>
-      </c>
-      <c r="S39" s="15"/>
-      <c r="T39" s="15" t="s">
-        <v>313</v>
-      </c>
-      <c r="U39" s="12"/>
-      <c r="V39" s="15" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="12" t="s">
-        <v>290</v>
-      </c>
-      <c r="B40" s="12" t="s">
-        <v>315</v>
-      </c>
-      <c r="C40" s="13" t="str">
-        <f aca="false">HYPERLINK("https://www.sourcepass.com/managed-it-services-denver","www.sourcepass.com/managed-it-services-denver")</f>
-        <v>www.sourcepass.com/managed-it-services-denver</v>
-      </c>
-      <c r="D40" s="12" t="s">
-        <v>316</v>
-      </c>
-      <c r="E40" s="14" t="n">
-        <v>2001</v>
-      </c>
-      <c r="F40" s="14" t="n">
-        <f aca="false">IF(E40="","",Method!$B$2-E40)</f>
-        <v>25</v>
-      </c>
-      <c r="G40" s="14" t="n">
-        <v>10</v>
-      </c>
-      <c r="H40" s="14" t="n">
-        <v>30</v>
-      </c>
-      <c r="I40" s="15" t="s">
-        <v>317</v>
-      </c>
-      <c r="J40" s="16" t="n">
-        <f aca="false">IF(G40="","",ROUND(G40*Method!$B$3/1000000,1))</f>
-        <v>1.5</v>
-      </c>
-      <c r="K40" s="16" t="n">
-        <f aca="false">IF(H40="","",ROUND(H40*Method!$B$4/1000000,1))</f>
-        <v>6</v>
-      </c>
-      <c r="L40" s="16" t="n">
-        <f aca="false">IF(J40="","",ROUND(J40*Method!$B$6*Method!$B$7,1))</f>
-        <v>0.9</v>
-      </c>
-      <c r="M40" s="16" t="n">
-        <f aca="false">IF(K40="","",ROUND(K40*Method!$B$6*Method!$B$8,1))</f>
-        <v>6.3</v>
-      </c>
-      <c r="N40" s="12"/>
-      <c r="O40" s="15" t="s">
-        <v>318</v>
-      </c>
-      <c r="P40" s="15" t="s">
-        <v>319</v>
-      </c>
-      <c r="Q40" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="R40" s="15" t="s">
-        <v>312</v>
-      </c>
-      <c r="S40" s="15"/>
-      <c r="T40" s="15" t="s">
-        <v>320</v>
-      </c>
-      <c r="U40" s="12"/>
-      <c r="V40" s="15"/>
-    </row>
-    <row r="41" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="12" t="s">
-        <v>290</v>
-      </c>
-      <c r="B41" s="12" t="s">
-        <v>321</v>
-      </c>
-      <c r="C41" s="13" t="str">
-        <f aca="false">HYPERLINK("https://www.verticomm.com","www.verticomm.com")</f>
-        <v>www.verticomm.com</v>
-      </c>
-      <c r="D41" s="12" t="s">
-        <v>322</v>
-      </c>
-      <c r="E41" s="14" t="n">
-        <v>1999</v>
-      </c>
-      <c r="F41" s="14" t="n">
-        <f aca="false">IF(E41="","",Method!$B$2-E41)</f>
-        <v>27</v>
-      </c>
-      <c r="G41" s="14" t="n">
-        <v>61</v>
-      </c>
-      <c r="H41" s="14" t="n">
-        <v>61</v>
-      </c>
-      <c r="I41" s="15" t="s">
-        <v>323</v>
-      </c>
-      <c r="J41" s="16" t="n">
-        <f aca="false">IF(G41="","",ROUND(G41*Method!$B$3/1000000,1))</f>
-        <v>9.2</v>
-      </c>
-      <c r="K41" s="16" t="n">
-        <f aca="false">IF(H41="","",ROUND(H41*Method!$B$4/1000000,1))</f>
-        <v>12.2</v>
-      </c>
-      <c r="L41" s="16" t="n">
-        <f aca="false">IF(J41="","",ROUND(J41*Method!$B$6*Method!$B$7,1))</f>
-        <v>5.5</v>
-      </c>
-      <c r="M41" s="16" t="n">
-        <f aca="false">IF(K41="","",ROUND(K41*Method!$B$6*Method!$B$8,1))</f>
-        <v>12.8</v>
-      </c>
-      <c r="N41" s="12"/>
-      <c r="O41" s="15" t="s">
-        <v>324</v>
-      </c>
-      <c r="P41" s="15" t="s">
-        <v>325</v>
-      </c>
-      <c r="Q41" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="R41" s="15" t="s">
-        <v>326</v>
-      </c>
-      <c r="S41" s="15"/>
-      <c r="T41" s="15" t="s">
-        <v>327</v>
-      </c>
-      <c r="U41" s="12"/>
-      <c r="V41" s="15" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="12" t="s">
-        <v>290</v>
-      </c>
-      <c r="B42" s="12" t="s">
-        <v>329</v>
-      </c>
-      <c r="C42" s="13" t="str">
-        <f aca="false">HYPERLINK("https://vertilocity.com","vertilocity.com")</f>
-        <v>vertilocity.com</v>
-      </c>
-      <c r="D42" s="12" t="s">
-        <v>330</v>
-      </c>
-      <c r="E42" s="14" t="n">
-        <v>2007</v>
       </c>
       <c r="F42" s="14" t="n">
         <f aca="false">IF(E42="","",Method!$B$2-E42)</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>50</v>
+        <v>375</v>
       </c>
       <c r="H42" s="14" t="n">
-        <v>185</v>
+        <v>375</v>
       </c>
       <c r="I42" s="15" t="s">
         <v>331</v>
       </c>
       <c r="J42" s="16" t="n">
         <f aca="false">IF(G42="","",ROUND(G42*Method!$B$3/1000000,1))</f>
-        <v>7.5</v>
+        <v>56.3</v>
       </c>
       <c r="K42" s="16" t="n">
         <f aca="false">IF(H42="","",ROUND(H42*Method!$B$4/1000000,1))</f>
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="L42" s="16" t="n">
         <f aca="false">IF(J42="","",ROUND(J42*Method!$B$6*Method!$B$7,1))</f>
-        <v>4.5</v>
+        <v>33.8</v>
       </c>
       <c r="M42" s="16" t="n">
         <f aca="false">IF(K42="","",ROUND(K42*Method!$B$6*Method!$B$8,1))</f>
-        <v>38.9</v>
+        <v>78.8</v>
       </c>
       <c r="N42" s="12"/>
       <c r="O42" s="15" t="s">
@@ -6521,7 +6778,7 @@
         <v>333</v>
       </c>
       <c r="Q42" s="12" t="s">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="R42" s="15" t="s">
         <v>334</v>
@@ -6535,368 +6792,365 @@
         <v>336</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
-        <v>290</v>
+        <v>312</v>
       </c>
       <c r="B43" s="12" t="s">
         <v>337</v>
       </c>
-      <c r="C43" s="12"/>
+      <c r="C43" s="13" t="str">
+        <f aca="false">HYPERLINK("https://www.sourcepass.com/managed-it-services-denver","www.sourcepass.com/managed-it-services-denver")</f>
+        <v>www.sourcepass.com/managed-it-services-denver</v>
+      </c>
       <c r="D43" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="E43" s="12"/>
-      <c r="F43" s="12"/>
+        <v>338</v>
+      </c>
+      <c r="E43" s="14" t="n">
+        <v>2001</v>
+      </c>
+      <c r="F43" s="14" t="n">
+        <f aca="false">IF(E43="","",Method!$B$2-E43)</f>
+        <v>25</v>
+      </c>
       <c r="G43" s="14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H43" s="14" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I43" s="15" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="J43" s="16" t="n">
         <f aca="false">IF(G43="","",ROUND(G43*Method!$B$3/1000000,1))</f>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="K43" s="16" t="n">
         <f aca="false">IF(H43="","",ROUND(H43*Method!$B$4/1000000,1))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L43" s="16" t="n">
         <f aca="false">IF(J43="","",ROUND(J43*Method!$B$6*Method!$B$7,1))</f>
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M43" s="16" t="n">
         <f aca="false">IF(K43="","",ROUND(K43*Method!$B$6*Method!$B$8,1))</f>
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="N43" s="12"/>
       <c r="O43" s="15" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="P43" s="15" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q43" s="12" t="s">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="R43" s="15" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="S43" s="15"/>
       <c r="T43" s="15" t="s">
         <v>342</v>
       </c>
       <c r="U43" s="12"/>
-      <c r="V43" s="15" t="s">
-        <v>343</v>
-      </c>
+      <c r="V43" s="15"/>
     </row>
     <row r="44" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>290</v>
+        <v>312</v>
       </c>
       <c r="B44" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="C44" s="13" t="str">
+        <f aca="false">HYPERLINK("https://www.verticomm.com","www.verticomm.com")</f>
+        <v>www.verticomm.com</v>
+      </c>
+      <c r="D44" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="C44" s="13" t="str">
+      <c r="E44" s="14" t="n">
+        <v>1999</v>
+      </c>
+      <c r="F44" s="14" t="n">
+        <f aca="false">IF(E44="","",Method!$B$2-E44)</f>
+        <v>27</v>
+      </c>
+      <c r="G44" s="14" t="n">
+        <v>61</v>
+      </c>
+      <c r="H44" s="14" t="n">
+        <v>61</v>
+      </c>
+      <c r="I44" s="15" t="s">
+        <v>345</v>
+      </c>
+      <c r="J44" s="16" t="n">
+        <f aca="false">IF(G44="","",ROUND(G44*Method!$B$3/1000000,1))</f>
+        <v>9.2</v>
+      </c>
+      <c r="K44" s="16" t="n">
+        <f aca="false">IF(H44="","",ROUND(H44*Method!$B$4/1000000,1))</f>
+        <v>12.2</v>
+      </c>
+      <c r="L44" s="16" t="n">
+        <f aca="false">IF(J44="","",ROUND(J44*Method!$B$6*Method!$B$7,1))</f>
+        <v>5.5</v>
+      </c>
+      <c r="M44" s="16" t="n">
+        <f aca="false">IF(K44="","",ROUND(K44*Method!$B$6*Method!$B$8,1))</f>
+        <v>12.8</v>
+      </c>
+      <c r="N44" s="12"/>
+      <c r="O44" s="15" t="s">
+        <v>346</v>
+      </c>
+      <c r="P44" s="15" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q44" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="R44" s="15" t="s">
+        <v>348</v>
+      </c>
+      <c r="S44" s="15"/>
+      <c r="T44" s="15" t="s">
+        <v>349</v>
+      </c>
+      <c r="U44" s="12"/>
+      <c r="V44" s="15" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="B45" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="C45" s="13" t="str">
+        <f aca="false">HYPERLINK("https://vertilocity.com","vertilocity.com")</f>
+        <v>vertilocity.com</v>
+      </c>
+      <c r="D45" s="12" t="s">
+        <v>352</v>
+      </c>
+      <c r="E45" s="14" t="n">
+        <v>2007</v>
+      </c>
+      <c r="F45" s="14" t="n">
+        <f aca="false">IF(E45="","",Method!$B$2-E45)</f>
+        <v>19</v>
+      </c>
+      <c r="G45" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="H45" s="14" t="n">
+        <v>185</v>
+      </c>
+      <c r="I45" s="15" t="s">
+        <v>353</v>
+      </c>
+      <c r="J45" s="16" t="n">
+        <f aca="false">IF(G45="","",ROUND(G45*Method!$B$3/1000000,1))</f>
+        <v>7.5</v>
+      </c>
+      <c r="K45" s="16" t="n">
+        <f aca="false">IF(H45="","",ROUND(H45*Method!$B$4/1000000,1))</f>
+        <v>37</v>
+      </c>
+      <c r="L45" s="16" t="n">
+        <f aca="false">IF(J45="","",ROUND(J45*Method!$B$6*Method!$B$7,1))</f>
+        <v>4.5</v>
+      </c>
+      <c r="M45" s="16" t="n">
+        <f aca="false">IF(K45="","",ROUND(K45*Method!$B$6*Method!$B$8,1))</f>
+        <v>38.9</v>
+      </c>
+      <c r="N45" s="12"/>
+      <c r="O45" s="15" t="s">
+        <v>354</v>
+      </c>
+      <c r="P45" s="15" t="s">
+        <v>355</v>
+      </c>
+      <c r="Q45" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="R45" s="15" t="s">
+        <v>356</v>
+      </c>
+      <c r="S45" s="15"/>
+      <c r="T45" s="15" t="s">
+        <v>357</v>
+      </c>
+      <c r="U45" s="12"/>
+      <c r="V45" s="15" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="B46" s="12" t="s">
+        <v>359</v>
+      </c>
+      <c r="C46" s="12"/>
+      <c r="D46" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E46" s="12"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="15" t="s">
+        <v>360</v>
+      </c>
+      <c r="J46" s="16" t="n">
+        <f aca="false">IF(G46="","",ROUND(G46*Method!$B$3/1000000,1))</f>
+        <v>0</v>
+      </c>
+      <c r="K46" s="16" t="n">
+        <f aca="false">IF(H46="","",ROUND(H46*Method!$B$4/1000000,1))</f>
+        <v>0</v>
+      </c>
+      <c r="L46" s="16" t="n">
+        <f aca="false">IF(J46="","",ROUND(J46*Method!$B$6*Method!$B$7,1))</f>
+        <v>0</v>
+      </c>
+      <c r="M46" s="16" t="n">
+        <f aca="false">IF(K46="","",ROUND(K46*Method!$B$6*Method!$B$8,1))</f>
+        <v>0</v>
+      </c>
+      <c r="N46" s="12"/>
+      <c r="O46" s="15" t="s">
+        <v>361</v>
+      </c>
+      <c r="P46" s="15" t="s">
+        <v>362</v>
+      </c>
+      <c r="Q46" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="R46" s="15" t="s">
+        <v>363</v>
+      </c>
+      <c r="S46" s="15"/>
+      <c r="T46" s="15" t="s">
+        <v>364</v>
+      </c>
+      <c r="U46" s="12"/>
+      <c r="V46" s="15" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="B47" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="C47" s="13" t="str">
         <f aca="false">HYPERLINK("https://www.ironedgegroup.com/service-areas/grand-junction/","www.ironedgegroup.com/service-areas/grand-junction")</f>
         <v>www.ironedgegroup.com/service-areas/grand-junction</v>
       </c>
-      <c r="D44" s="12" t="s">
-        <v>345</v>
-      </c>
-      <c r="E44" s="14" t="n">
+      <c r="D47" s="12" t="s">
+        <v>367</v>
+      </c>
+      <c r="E47" s="14" t="n">
         <v>2003</v>
       </c>
-      <c r="F44" s="14" t="n">
-        <f aca="false">IF(E44="","",Method!$B$2-E44)</f>
+      <c r="F47" s="14" t="n">
+        <f aca="false">IF(E47="","",Method!$B$2-E47)</f>
         <v>23</v>
       </c>
-      <c r="G44" s="14" t="n">
+      <c r="G47" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="H44" s="14" t="n">
+      <c r="H47" s="14" t="n">
         <v>50</v>
       </c>
-      <c r="I44" s="15" t="s">
-        <v>346</v>
-      </c>
-      <c r="J44" s="16" t="n">
-        <f aca="false">IF(G44="","",ROUND(G44*Method!$B$3/1000000,1))</f>
+      <c r="I47" s="15" t="s">
+        <v>368</v>
+      </c>
+      <c r="J47" s="16" t="n">
+        <f aca="false">IF(G47="","",ROUND(G47*Method!$B$3/1000000,1))</f>
         <v>1.5</v>
       </c>
-      <c r="K44" s="16" t="n">
-        <f aca="false">IF(H44="","",ROUND(H44*Method!$B$4/1000000,1))</f>
+      <c r="K47" s="16" t="n">
+        <f aca="false">IF(H47="","",ROUND(H47*Method!$B$4/1000000,1))</f>
         <v>10</v>
       </c>
-      <c r="L44" s="16" t="n">
-        <f aca="false">IF(J44="","",ROUND(J44*Method!$B$6*Method!$B$7,1))</f>
+      <c r="L47" s="16" t="n">
+        <f aca="false">IF(J47="","",ROUND(J47*Method!$B$6*Method!$B$7,1))</f>
         <v>0.9</v>
       </c>
-      <c r="M44" s="16" t="n">
-        <f aca="false">IF(K44="","",ROUND(K44*Method!$B$6*Method!$B$8,1))</f>
+      <c r="M47" s="16" t="n">
+        <f aca="false">IF(K47="","",ROUND(K47*Method!$B$6*Method!$B$8,1))</f>
         <v>10.5</v>
       </c>
-      <c r="N44" s="12"/>
-      <c r="O44" s="15" t="s">
-        <v>347</v>
-      </c>
-      <c r="P44" s="15" t="s">
-        <v>348</v>
-      </c>
-      <c r="Q44" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="R44" s="15" t="s">
-        <v>349</v>
-      </c>
-      <c r="S44" s="15"/>
-      <c r="T44" s="15" t="s">
-        <v>350</v>
-      </c>
-      <c r="U44" s="12"/>
-      <c r="V44" s="15" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="12" t="s">
-        <v>290</v>
-      </c>
-      <c r="B45" s="12" t="s">
-        <v>352</v>
-      </c>
-      <c r="C45" s="13" t="str">
+      <c r="N47" s="12"/>
+      <c r="O47" s="15" t="s">
+        <v>369</v>
+      </c>
+      <c r="P47" s="15" t="s">
+        <v>370</v>
+      </c>
+      <c r="Q47" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="R47" s="15" t="s">
+        <v>371</v>
+      </c>
+      <c r="S47" s="15"/>
+      <c r="T47" s="15" t="s">
+        <v>372</v>
+      </c>
+      <c r="U47" s="12"/>
+      <c r="V47" s="15" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="B48" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="C48" s="13" t="str">
         <f aca="false">HYPERLINK("https://commwestcorp.com","commwestcorp.com")</f>
         <v>commwestcorp.com</v>
       </c>
-      <c r="D45" s="12" t="s">
-        <v>353</v>
-      </c>
-      <c r="E45" s="14" t="n">
+      <c r="D48" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="E48" s="14" t="n">
         <v>2002</v>
-      </c>
-      <c r="F45" s="14" t="n">
-        <f aca="false">IF(E45="","",Method!$B$2-E45)</f>
-        <v>24</v>
-      </c>
-      <c r="G45" s="14" t="n">
-        <v>10</v>
-      </c>
-      <c r="H45" s="14" t="n">
-        <v>25</v>
-      </c>
-      <c r="I45" s="15" t="s">
-        <v>354</v>
-      </c>
-      <c r="J45" s="16" t="n">
-        <f aca="false">IF(G45="","",ROUND(G45*Method!$B$3/1000000,1))</f>
-        <v>1.5</v>
-      </c>
-      <c r="K45" s="16" t="n">
-        <f aca="false">IF(H45="","",ROUND(H45*Method!$B$4/1000000,1))</f>
-        <v>5</v>
-      </c>
-      <c r="L45" s="16" t="n">
-        <f aca="false">IF(J45="","",ROUND(J45*Method!$B$6*Method!$B$7,1))</f>
-        <v>0.9</v>
-      </c>
-      <c r="M45" s="16" t="n">
-        <f aca="false">IF(K45="","",ROUND(K45*Method!$B$6*Method!$B$8,1))</f>
-        <v>5.3</v>
-      </c>
-      <c r="N45" s="12"/>
-      <c r="O45" s="15" t="s">
-        <v>355</v>
-      </c>
-      <c r="P45" s="15" t="s">
-        <v>356</v>
-      </c>
-      <c r="Q45" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="R45" s="15" t="s">
-        <v>357</v>
-      </c>
-      <c r="S45" s="15"/>
-      <c r="T45" s="15" t="s">
-        <v>358</v>
-      </c>
-      <c r="U45" s="12"/>
-      <c r="V45" s="15" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="12" t="s">
-        <v>290</v>
-      </c>
-      <c r="B46" s="12" t="s">
-        <v>360</v>
-      </c>
-      <c r="C46" s="13" t="str">
-        <f aca="false">HYPERLINK("https://www.appliedtech.us","www.appliedtech.us")</f>
-        <v>www.appliedtech.us</v>
-      </c>
-      <c r="D46" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="E46" s="14" t="n">
-        <v>1999</v>
-      </c>
-      <c r="F46" s="14" t="n">
-        <f aca="false">IF(E46="","",Method!$B$2-E46)</f>
-        <v>27</v>
-      </c>
-      <c r="G46" s="14" t="n">
-        <v>50</v>
-      </c>
-      <c r="H46" s="14" t="n">
-        <v>99</v>
-      </c>
-      <c r="I46" s="15" t="s">
-        <v>362</v>
-      </c>
-      <c r="J46" s="16" t="n">
-        <f aca="false">IF(G46="","",ROUND(G46*Method!$B$3/1000000,1))</f>
-        <v>7.5</v>
-      </c>
-      <c r="K46" s="16" t="n">
-        <f aca="false">IF(H46="","",ROUND(H46*Method!$B$4/1000000,1))</f>
-        <v>19.8</v>
-      </c>
-      <c r="L46" s="16" t="n">
-        <f aca="false">IF(J46="","",ROUND(J46*Method!$B$6*Method!$B$7,1))</f>
-        <v>4.5</v>
-      </c>
-      <c r="M46" s="16" t="n">
-        <f aca="false">IF(K46="","",ROUND(K46*Method!$B$6*Method!$B$8,1))</f>
-        <v>20.8</v>
-      </c>
-      <c r="N46" s="12"/>
-      <c r="O46" s="15" t="s">
-        <v>363</v>
-      </c>
-      <c r="P46" s="15" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q46" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="R46" s="15" t="s">
-        <v>364</v>
-      </c>
-      <c r="S46" s="15"/>
-      <c r="T46" s="15" t="s">
-        <v>365</v>
-      </c>
-      <c r="U46" s="12" t="s">
-        <v>366</v>
-      </c>
-      <c r="V46" s="15" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="12" t="s">
-        <v>290</v>
-      </c>
-      <c r="B47" s="12" t="s">
-        <v>368</v>
-      </c>
-      <c r="C47" s="13" t="str">
-        <f aca="false">HYPERLINK("https://pei.com","pei.com")</f>
-        <v>pei.com</v>
-      </c>
-      <c r="D47" s="12" t="s">
-        <v>244</v>
-      </c>
-      <c r="E47" s="14" t="n">
-        <v>1988</v>
-      </c>
-      <c r="F47" s="14" t="n">
-        <f aca="false">IF(E47="","",Method!$B$2-E47)</f>
-        <v>38</v>
-      </c>
-      <c r="G47" s="14" t="n">
-        <v>20</v>
-      </c>
-      <c r="H47" s="14" t="n">
-        <v>40</v>
-      </c>
-      <c r="I47" s="15" t="s">
-        <v>369</v>
-      </c>
-      <c r="J47" s="16" t="n">
-        <f aca="false">IF(G47="","",ROUND(G47*Method!$B$3/1000000,1))</f>
-        <v>3</v>
-      </c>
-      <c r="K47" s="16" t="n">
-        <f aca="false">IF(H47="","",ROUND(H47*Method!$B$4/1000000,1))</f>
-        <v>8</v>
-      </c>
-      <c r="L47" s="16" t="n">
-        <f aca="false">IF(J47="","",ROUND(J47*Method!$B$6*Method!$B$7,1))</f>
-        <v>1.8</v>
-      </c>
-      <c r="M47" s="16" t="n">
-        <f aca="false">IF(K47="","",ROUND(K47*Method!$B$6*Method!$B$8,1))</f>
-        <v>8.4</v>
-      </c>
-      <c r="N47" s="12"/>
-      <c r="O47" s="15" t="s">
-        <v>370</v>
-      </c>
-      <c r="P47" s="15" t="s">
-        <v>371</v>
-      </c>
-      <c r="Q47" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="R47" s="15" t="s">
-        <v>372</v>
-      </c>
-      <c r="S47" s="15" t="s">
-        <v>373</v>
-      </c>
-      <c r="T47" s="15" t="s">
-        <v>374</v>
-      </c>
-      <c r="U47" s="12"/>
-      <c r="V47" s="15" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="12" t="s">
-        <v>290</v>
-      </c>
-      <c r="B48" s="12" t="s">
-        <v>376</v>
-      </c>
-      <c r="C48" s="12"/>
-      <c r="D48" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="E48" s="14" t="n">
-        <v>2001</v>
       </c>
       <c r="F48" s="14" t="n">
         <f aca="false">IF(E48="","",Method!$B$2-E48)</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G48" s="14" t="n">
         <v>10</v>
       </c>
       <c r="H48" s="14" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I48" s="15" t="s">
-        <v>261</v>
+        <v>376</v>
       </c>
       <c r="J48" s="16" t="n">
         <f aca="false">IF(G48="","",ROUND(G48*Method!$B$3/1000000,1))</f>
@@ -6904,7 +7158,7 @@
       </c>
       <c r="K48" s="16" t="n">
         <f aca="false">IF(H48="","",ROUND(H48*Method!$B$4/1000000,1))</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L48" s="16" t="n">
         <f aca="false">IF(J48="","",ROUND(J48*Method!$B$6*Method!$B$7,1))</f>
@@ -6912,7 +7166,7 @@
       </c>
       <c r="M48" s="16" t="n">
         <f aca="false">IF(K48="","",ROUND(K48*Method!$B$6*Method!$B$8,1))</f>
-        <v>6.3</v>
+        <v>5.3</v>
       </c>
       <c r="N48" s="12"/>
       <c r="O48" s="15" t="s">
@@ -6922,327 +7176,532 @@
         <v>378</v>
       </c>
       <c r="Q48" s="12" t="s">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="R48" s="15" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="S48" s="15"/>
       <c r="T48" s="15" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="U48" s="12"/>
       <c r="V48" s="15" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="12" t="s">
-        <v>290</v>
+        <v>312</v>
       </c>
       <c r="B49" s="12" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C49" s="13" t="str">
+        <f aca="false">HYPERLINK("https://www.appliedtech.us","www.appliedtech.us")</f>
+        <v>www.appliedtech.us</v>
+      </c>
+      <c r="D49" s="12" t="s">
+        <v>383</v>
+      </c>
+      <c r="E49" s="14" t="n">
+        <v>1999</v>
+      </c>
+      <c r="F49" s="14" t="n">
+        <f aca="false">IF(E49="","",Method!$B$2-E49)</f>
+        <v>27</v>
+      </c>
+      <c r="G49" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="H49" s="14" t="n">
+        <v>99</v>
+      </c>
+      <c r="I49" s="15" t="s">
+        <v>384</v>
+      </c>
+      <c r="J49" s="16" t="n">
+        <f aca="false">IF(G49="","",ROUND(G49*Method!$B$3/1000000,1))</f>
+        <v>7.5</v>
+      </c>
+      <c r="K49" s="16" t="n">
+        <f aca="false">IF(H49="","",ROUND(H49*Method!$B$4/1000000,1))</f>
+        <v>19.8</v>
+      </c>
+      <c r="L49" s="16" t="n">
+        <f aca="false">IF(J49="","",ROUND(J49*Method!$B$6*Method!$B$7,1))</f>
+        <v>4.5</v>
+      </c>
+      <c r="M49" s="16" t="n">
+        <f aca="false">IF(K49="","",ROUND(K49*Method!$B$6*Method!$B$8,1))</f>
+        <v>20.8</v>
+      </c>
+      <c r="N49" s="12"/>
+      <c r="O49" s="15" t="s">
+        <v>385</v>
+      </c>
+      <c r="P49" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q49" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="R49" s="15" t="s">
+        <v>386</v>
+      </c>
+      <c r="S49" s="15"/>
+      <c r="T49" s="15" t="s">
+        <v>387</v>
+      </c>
+      <c r="U49" s="12" t="s">
+        <v>388</v>
+      </c>
+      <c r="V49" s="15" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="B50" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="C50" s="13" t="str">
+        <f aca="false">HYPERLINK("https://pei.com","pei.com")</f>
+        <v>pei.com</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="E50" s="14" t="n">
+        <v>1988</v>
+      </c>
+      <c r="F50" s="14" t="n">
+        <f aca="false">IF(E50="","",Method!$B$2-E50)</f>
+        <v>38</v>
+      </c>
+      <c r="G50" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="H50" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="I50" s="15" t="s">
+        <v>391</v>
+      </c>
+      <c r="J50" s="16" t="n">
+        <f aca="false">IF(G50="","",ROUND(G50*Method!$B$3/1000000,1))</f>
+        <v>3</v>
+      </c>
+      <c r="K50" s="16" t="n">
+        <f aca="false">IF(H50="","",ROUND(H50*Method!$B$4/1000000,1))</f>
+        <v>8</v>
+      </c>
+      <c r="L50" s="16" t="n">
+        <f aca="false">IF(J50="","",ROUND(J50*Method!$B$6*Method!$B$7,1))</f>
+        <v>1.8</v>
+      </c>
+      <c r="M50" s="16" t="n">
+        <f aca="false">IF(K50="","",ROUND(K50*Method!$B$6*Method!$B$8,1))</f>
+        <v>8.4</v>
+      </c>
+      <c r="N50" s="12"/>
+      <c r="O50" s="15" t="s">
+        <v>392</v>
+      </c>
+      <c r="P50" s="15" t="s">
+        <v>393</v>
+      </c>
+      <c r="Q50" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="R50" s="15" t="s">
+        <v>394</v>
+      </c>
+      <c r="S50" s="15" t="s">
+        <v>395</v>
+      </c>
+      <c r="T50" s="15" t="s">
+        <v>396</v>
+      </c>
+      <c r="U50" s="12"/>
+      <c r="V50" s="15" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="B51" s="12" t="s">
+        <v>398</v>
+      </c>
+      <c r="C51" s="12"/>
+      <c r="D51" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="E51" s="14" t="n">
+        <v>2001</v>
+      </c>
+      <c r="F51" s="14" t="n">
+        <f aca="false">IF(E51="","",Method!$B$2-E51)</f>
+        <v>25</v>
+      </c>
+      <c r="G51" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="H51" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="I51" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="J51" s="16" t="n">
+        <f aca="false">IF(G51="","",ROUND(G51*Method!$B$3/1000000,1))</f>
+        <v>1.5</v>
+      </c>
+      <c r="K51" s="16" t="n">
+        <f aca="false">IF(H51="","",ROUND(H51*Method!$B$4/1000000,1))</f>
+        <v>6</v>
+      </c>
+      <c r="L51" s="16" t="n">
+        <f aca="false">IF(J51="","",ROUND(J51*Method!$B$6*Method!$B$7,1))</f>
+        <v>0.9</v>
+      </c>
+      <c r="M51" s="16" t="n">
+        <f aca="false">IF(K51="","",ROUND(K51*Method!$B$6*Method!$B$8,1))</f>
+        <v>6.3</v>
+      </c>
+      <c r="N51" s="12"/>
+      <c r="O51" s="15" t="s">
+        <v>399</v>
+      </c>
+      <c r="P51" s="15" t="s">
+        <v>400</v>
+      </c>
+      <c r="Q51" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="R51" s="15" t="s">
+        <v>356</v>
+      </c>
+      <c r="S51" s="15"/>
+      <c r="T51" s="15" t="s">
+        <v>401</v>
+      </c>
+      <c r="U51" s="12"/>
+      <c r="V51" s="15" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="B52" s="12" t="s">
+        <v>403</v>
+      </c>
+      <c r="C52" s="13" t="str">
         <f aca="false">HYPERLINK("https://optimumnetworking.com","optimumnetworking.com")</f>
         <v>optimumnetworking.com</v>
       </c>
-      <c r="D49" s="12" t="s">
-        <v>382</v>
-      </c>
-      <c r="E49" s="14" t="n">
+      <c r="D52" s="12" t="s">
+        <v>404</v>
+      </c>
+      <c r="E52" s="14" t="n">
         <v>1995</v>
       </c>
-      <c r="F49" s="14" t="n">
-        <f aca="false">IF(E49="","",Method!$B$2-E49)</f>
+      <c r="F52" s="14" t="n">
+        <f aca="false">IF(E52="","",Method!$B$2-E52)</f>
         <v>31</v>
       </c>
-      <c r="G49" s="14" t="n">
+      <c r="G52" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="H49" s="14" t="n">
+      <c r="H52" s="14" t="n">
         <v>30</v>
       </c>
-      <c r="I49" s="15" t="s">
-        <v>261</v>
-      </c>
-      <c r="J49" s="16" t="n">
-        <f aca="false">IF(G49="","",ROUND(G49*Method!$B$3/1000000,1))</f>
+      <c r="I52" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="J52" s="16" t="n">
+        <f aca="false">IF(G52="","",ROUND(G52*Method!$B$3/1000000,1))</f>
         <v>1.5</v>
       </c>
-      <c r="K49" s="16" t="n">
-        <f aca="false">IF(H49="","",ROUND(H49*Method!$B$4/1000000,1))</f>
+      <c r="K52" s="16" t="n">
+        <f aca="false">IF(H52="","",ROUND(H52*Method!$B$4/1000000,1))</f>
         <v>6</v>
       </c>
-      <c r="L49" s="16" t="n">
-        <f aca="false">IF(J49="","",ROUND(J49*Method!$B$6*Method!$B$7,1))</f>
+      <c r="L52" s="16" t="n">
+        <f aca="false">IF(J52="","",ROUND(J52*Method!$B$6*Method!$B$7,1))</f>
         <v>0.9</v>
       </c>
-      <c r="M49" s="16" t="n">
-        <f aca="false">IF(K49="","",ROUND(K49*Method!$B$6*Method!$B$8,1))</f>
+      <c r="M52" s="16" t="n">
+        <f aca="false">IF(K52="","",ROUND(K52*Method!$B$6*Method!$B$8,1))</f>
         <v>6.3</v>
       </c>
-      <c r="N49" s="12"/>
-      <c r="O49" s="15" t="s">
-        <v>383</v>
-      </c>
-      <c r="P49" s="15" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q49" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="R49" s="15" t="s">
-        <v>334</v>
-      </c>
-      <c r="S49" s="15"/>
-      <c r="T49" s="15" t="s">
-        <v>384</v>
-      </c>
-      <c r="U49" s="12" t="s">
-        <v>385</v>
-      </c>
-      <c r="V49" s="15" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="17" t="s">
-        <v>387</v>
-      </c>
-      <c r="B50" s="17" t="s">
-        <v>388</v>
-      </c>
-      <c r="C50" s="18" t="str">
+      <c r="N52" s="12"/>
+      <c r="O52" s="15" t="s">
+        <v>405</v>
+      </c>
+      <c r="P52" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q52" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="R52" s="15" t="s">
+        <v>356</v>
+      </c>
+      <c r="S52" s="15"/>
+      <c r="T52" s="15" t="s">
+        <v>406</v>
+      </c>
+      <c r="U52" s="12" t="s">
+        <v>407</v>
+      </c>
+      <c r="V52" s="15" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="17" t="s">
+        <v>409</v>
+      </c>
+      <c r="B53" s="17" t="s">
+        <v>410</v>
+      </c>
+      <c r="C53" s="18" t="str">
         <f aca="false">HYPERLINK("https://www.teamlogicit.com/denverco610","www.teamlogicit.com/denverco610")</f>
         <v>www.teamlogicit.com/denverco610</v>
       </c>
-      <c r="D50" s="17" t="s">
+      <c r="D53" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="E50" s="17"/>
-      <c r="F50" s="17"/>
-      <c r="G50" s="19" t="n">
+      <c r="E53" s="17"/>
+      <c r="F53" s="17"/>
+      <c r="G53" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="H50" s="19" t="n">
+      <c r="H53" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="I50" s="20" t="s">
-        <v>389</v>
-      </c>
-      <c r="J50" s="21" t="n">
-        <f aca="false">IF(G50="","",ROUND(G50*Method!$B$3/1000000,1))</f>
+      <c r="I53" s="20" t="s">
+        <v>411</v>
+      </c>
+      <c r="J53" s="21" t="n">
+        <f aca="false">IF(G53="","",ROUND(G53*Method!$B$3/1000000,1))</f>
         <v>0.3</v>
       </c>
-      <c r="K50" s="21" t="n">
-        <f aca="false">IF(H50="","",ROUND(H50*Method!$B$4/1000000,1))</f>
+      <c r="K53" s="21" t="n">
+        <f aca="false">IF(H53="","",ROUND(H53*Method!$B$4/1000000,1))</f>
         <v>1.8</v>
       </c>
-      <c r="L50" s="21" t="n">
-        <f aca="false">IF(J50="","",ROUND(J50*Method!$B$6*Method!$B$7,1))</f>
+      <c r="L53" s="21" t="n">
+        <f aca="false">IF(J53="","",ROUND(J53*Method!$B$6*Method!$B$7,1))</f>
         <v>0.2</v>
       </c>
-      <c r="M50" s="21" t="n">
-        <f aca="false">IF(K50="","",ROUND(K50*Method!$B$6*Method!$B$8,1))</f>
+      <c r="M53" s="21" t="n">
+        <f aca="false">IF(K53="","",ROUND(K53*Method!$B$6*Method!$B$8,1))</f>
         <v>1.9</v>
       </c>
-      <c r="N50" s="17"/>
-      <c r="O50" s="20" t="s">
-        <v>390</v>
-      </c>
-      <c r="P50" s="20" t="s">
-        <v>391</v>
-      </c>
-      <c r="Q50" s="17" t="s">
+      <c r="N53" s="17"/>
+      <c r="O53" s="20" t="s">
+        <v>412</v>
+      </c>
+      <c r="P53" s="20" t="s">
+        <v>413</v>
+      </c>
+      <c r="Q53" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="R50" s="20" t="s">
-        <v>392</v>
-      </c>
-      <c r="S50" s="20"/>
-      <c r="T50" s="20" t="s">
-        <v>393</v>
-      </c>
-      <c r="U50" s="17"/>
-      <c r="V50" s="20" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="17" t="s">
-        <v>387</v>
-      </c>
-      <c r="B51" s="17" t="s">
-        <v>395</v>
-      </c>
-      <c r="C51" s="18" t="str">
+      <c r="R53" s="20" t="s">
+        <v>414</v>
+      </c>
+      <c r="S53" s="20"/>
+      <c r="T53" s="20" t="s">
+        <v>415</v>
+      </c>
+      <c r="U53" s="17"/>
+      <c r="V53" s="20" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="17" t="s">
+        <v>409</v>
+      </c>
+      <c r="B54" s="17" t="s">
+        <v>417</v>
+      </c>
+      <c r="C54" s="18" t="str">
         <f aca="false">HYPERLINK("https://teamlogicit.com","teamlogicit.com")</f>
         <v>teamlogicit.com</v>
       </c>
-      <c r="D51" s="17" t="s">
+      <c r="D54" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="E51" s="19" t="n">
+      <c r="E54" s="19" t="n">
         <v>2011</v>
       </c>
-      <c r="F51" s="19" t="n">
-        <f aca="false">IF(E51="","",Method!$B$2-E51)</f>
+      <c r="F54" s="19" t="n">
+        <f aca="false">IF(E54="","",Method!$B$2-E54)</f>
         <v>15</v>
       </c>
-      <c r="G51" s="19" t="n">
+      <c r="G54" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="H51" s="19" t="n">
+      <c r="H54" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="I51" s="20" t="s">
-        <v>396</v>
-      </c>
-      <c r="J51" s="21" t="n">
-        <f aca="false">IF(G51="","",ROUND(G51*Method!$B$3/1000000,1))</f>
+      <c r="I54" s="20" t="s">
+        <v>418</v>
+      </c>
+      <c r="J54" s="21" t="n">
+        <f aca="false">IF(G54="","",ROUND(G54*Method!$B$3/1000000,1))</f>
         <v>0.3</v>
       </c>
-      <c r="K51" s="21" t="n">
-        <f aca="false">IF(H51="","",ROUND(H51*Method!$B$4/1000000,1))</f>
+      <c r="K54" s="21" t="n">
+        <f aca="false">IF(H54="","",ROUND(H54*Method!$B$4/1000000,1))</f>
         <v>1.8</v>
       </c>
-      <c r="L51" s="21" t="n">
-        <f aca="false">IF(J51="","",ROUND(J51*Method!$B$6*Method!$B$7,1))</f>
+      <c r="L54" s="21" t="n">
+        <f aca="false">IF(J54="","",ROUND(J54*Method!$B$6*Method!$B$7,1))</f>
         <v>0.2</v>
       </c>
-      <c r="M51" s="21" t="n">
-        <f aca="false">IF(K51="","",ROUND(K51*Method!$B$6*Method!$B$8,1))</f>
+      <c r="M54" s="21" t="n">
+        <f aca="false">IF(K54="","",ROUND(K54*Method!$B$6*Method!$B$8,1))</f>
         <v>1.9</v>
       </c>
-      <c r="N51" s="17"/>
-      <c r="O51" s="20" t="s">
-        <v>397</v>
-      </c>
-      <c r="P51" s="20" t="s">
-        <v>391</v>
-      </c>
-      <c r="Q51" s="17" t="s">
+      <c r="N54" s="17"/>
+      <c r="O54" s="20" t="s">
+        <v>419</v>
+      </c>
+      <c r="P54" s="20" t="s">
+        <v>413</v>
+      </c>
+      <c r="Q54" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="R51" s="20" t="s">
-        <v>392</v>
-      </c>
-      <c r="S51" s="20"/>
-      <c r="T51" s="20" t="s">
-        <v>398</v>
-      </c>
-      <c r="U51" s="17"/>
-      <c r="V51" s="20" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>400</v>
-      </c>
-      <c r="C52" s="8" t="str">
+      <c r="R54" s="20" t="s">
+        <v>414</v>
+      </c>
+      <c r="S54" s="20"/>
+      <c r="T54" s="20" t="s">
+        <v>420</v>
+      </c>
+      <c r="U54" s="17"/>
+      <c r="V54" s="20" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="C55" s="8" t="str">
         <f aca="false">HYPERLINK("https://coremanaged.com","coremanaged.com")</f>
         <v>coremanaged.com</v>
       </c>
-      <c r="D52" s="7" t="s">
+      <c r="D55" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E52" s="7"/>
-      <c r="F52" s="7"/>
-      <c r="G52" s="7"/>
-      <c r="H52" s="7"/>
-      <c r="I52" s="10"/>
-      <c r="J52" s="7"/>
-      <c r="K52" s="7"/>
-      <c r="L52" s="7"/>
-      <c r="M52" s="7"/>
-      <c r="N52" s="7"/>
-      <c r="O52" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="P52" s="10" t="s">
-        <v>195</v>
-      </c>
-      <c r="Q52" s="7" t="s">
+      <c r="E55" s="7"/>
+      <c r="F55" s="7"/>
+      <c r="G55" s="7"/>
+      <c r="H55" s="7"/>
+      <c r="I55" s="10"/>
+      <c r="J55" s="7"/>
+      <c r="K55" s="7"/>
+      <c r="L55" s="7"/>
+      <c r="M55" s="7"/>
+      <c r="N55" s="7"/>
+      <c r="O55" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="P55" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q55" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="R52" s="10"/>
-      <c r="S52" s="10"/>
-      <c r="T52" s="10" t="s">
-        <v>401</v>
-      </c>
-      <c r="U52" s="7"/>
-      <c r="V52" s="10"/>
-    </row>
-    <row r="53" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="B53" s="7" t="s">
-        <v>402</v>
-      </c>
-      <c r="C53" s="8" t="str">
+      <c r="R55" s="10"/>
+      <c r="S55" s="10"/>
+      <c r="T55" s="10" t="s">
+        <v>423</v>
+      </c>
+      <c r="U55" s="7"/>
+      <c r="V55" s="10"/>
+    </row>
+    <row r="56" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="C56" s="8" t="str">
         <f aca="false">HYPERLINK("https://www.coinfotech.com","www.coinfotech.com")</f>
         <v>www.coinfotech.com</v>
       </c>
-      <c r="D53" s="7" t="s">
+      <c r="D56" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="E53" s="7"/>
-      <c r="F53" s="7"/>
-      <c r="G53" s="9" t="n">
+      <c r="E56" s="7"/>
+      <c r="F56" s="7"/>
+      <c r="G56" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="H53" s="9" t="n">
+      <c r="H56" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="I53" s="10" t="s">
-        <v>403</v>
-      </c>
-      <c r="J53" s="11" t="n">
-        <f aca="false">IF(G53="","",ROUND(G53*Method!$B$3/1000000,1))</f>
+      <c r="I56" s="10" t="s">
+        <v>425</v>
+      </c>
+      <c r="J56" s="11" t="n">
+        <f aca="false">IF(G56="","",ROUND(G56*Method!$B$3/1000000,1))</f>
         <v>0.3</v>
       </c>
-      <c r="K53" s="11" t="n">
-        <f aca="false">IF(H53="","",ROUND(H53*Method!$B$4/1000000,1))</f>
+      <c r="K56" s="11" t="n">
+        <f aca="false">IF(H56="","",ROUND(H56*Method!$B$4/1000000,1))</f>
         <v>4</v>
       </c>
-      <c r="L53" s="11" t="n">
-        <f aca="false">IF(J53="","",ROUND(J53*Method!$B$6*Method!$B$7,1))</f>
+      <c r="L56" s="11" t="n">
+        <f aca="false">IF(J56="","",ROUND(J56*Method!$B$6*Method!$B$7,1))</f>
         <v>0.2</v>
       </c>
-      <c r="M53" s="11" t="n">
-        <f aca="false">IF(K53="","",ROUND(K53*Method!$B$6*Method!$B$8,1))</f>
+      <c r="M56" s="11" t="n">
+        <f aca="false">IF(K56="","",ROUND(K56*Method!$B$6*Method!$B$8,1))</f>
         <v>4.2</v>
       </c>
-      <c r="N53" s="7"/>
-      <c r="O53" s="10" t="s">
-        <v>195</v>
-      </c>
-      <c r="P53" s="10" t="s">
-        <v>404</v>
-      </c>
-      <c r="Q53" s="7" t="s">
+      <c r="N56" s="7"/>
+      <c r="O56" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="P56" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="Q56" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="R53" s="10" t="s">
-        <v>405</v>
-      </c>
-      <c r="S53" s="10"/>
-      <c r="T53" s="10" t="s">
-        <v>406</v>
-      </c>
-      <c r="U53" s="7"/>
-      <c r="V53" s="10" t="s">
-        <v>407</v>
+      <c r="R56" s="10" t="s">
+        <v>427</v>
+      </c>
+      <c r="S56" s="10"/>
+      <c r="T56" s="10" t="s">
+        <v>428</v>
+      </c>
+      <c r="U56" s="7"/>
+      <c r="V56" s="10" t="s">
+        <v>429</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V53"/>
+  <autoFilter ref="A1:V56"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -7259,7 +7718,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -7277,7 +7736,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>408</v>
+        <v>430</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -7286,7 +7745,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>409</v>
+        <v>431</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>15</v>
@@ -7295,22 +7754,22 @@
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>410</v>
+        <v>432</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>411</v>
+        <v>433</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>412</v>
+        <v>434</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>413</v>
+        <v>435</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>415</v>
+        <v>437</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7318,35 +7777,35 @@
         <v>28</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>416</v>
+        <v>438</v>
       </c>
       <c r="C2" s="8" t="str">
         <f aca="false">HYPERLINK("https://arielitservices.com","arielitservices.com")</f>
         <v>arielitservices.com</v>
       </c>
       <c r="D2" s="23" t="s">
-        <v>417</v>
+        <v>439</v>
       </c>
       <c r="E2" s="24" t="n">
         <v>2010</v>
       </c>
       <c r="F2" s="23" t="s">
-        <v>418</v>
+        <v>440</v>
       </c>
       <c r="G2" s="23" t="s">
-        <v>419</v>
+        <v>441</v>
       </c>
       <c r="H2" s="24" t="s">
-        <v>420</v>
+        <v>442</v>
       </c>
       <c r="I2" s="24" t="s">
-        <v>421</v>
+        <v>443</v>
       </c>
       <c r="J2" s="24" t="s">
-        <v>422</v>
+        <v>444</v>
       </c>
       <c r="K2" s="24" t="s">
-        <v>423</v>
+        <v>445</v>
       </c>
       <c r="L2" s="24"/>
     </row>
@@ -7368,25 +7827,25 @@
         <v>1993</v>
       </c>
       <c r="F3" s="23" t="s">
-        <v>424</v>
+        <v>446</v>
       </c>
       <c r="G3" s="23" t="s">
-        <v>425</v>
+        <v>447</v>
       </c>
       <c r="H3" s="24" t="s">
-        <v>426</v>
+        <v>448</v>
       </c>
       <c r="I3" s="24" t="s">
-        <v>427</v>
+        <v>449</v>
       </c>
       <c r="J3" s="24" t="s">
-        <v>428</v>
+        <v>450</v>
       </c>
       <c r="K3" s="24" t="s">
-        <v>429</v>
+        <v>451</v>
       </c>
       <c r="L3" s="24" t="s">
-        <v>430</v>
+        <v>452</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7394,41 +7853,41 @@
         <v>28</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>243</v>
+        <v>265</v>
       </c>
       <c r="C4" s="8" t="str">
         <f aca="false">HYPERLINK("https://windwardnetworks.com","windwardnetworks.com")</f>
         <v>windwardnetworks.com</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>431</v>
+        <v>453</v>
       </c>
       <c r="E4" s="24" t="n">
         <v>2004</v>
       </c>
       <c r="F4" s="23" t="s">
-        <v>432</v>
+        <v>454</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>433</v>
+        <v>455</v>
       </c>
       <c r="H4" s="24" t="s">
-        <v>434</v>
+        <v>456</v>
       </c>
       <c r="I4" s="24" t="s">
-        <v>435</v>
+        <v>457</v>
       </c>
       <c r="J4" s="24" t="s">
-        <v>436</v>
+        <v>458</v>
       </c>
       <c r="K4" s="24" t="s">
-        <v>437</v>
+        <v>459</v>
       </c>
       <c r="L4" s="24"/>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="25" t="s">
-        <v>438</v>
+        <v>460</v>
       </c>
       <c r="B5" s="23" t="s">
         <v>34</v>
@@ -7444,109 +7903,109 @@
         <v>1998</v>
       </c>
       <c r="F5" s="23" t="s">
-        <v>439</v>
+        <v>461</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>440</v>
+        <v>462</v>
       </c>
       <c r="H5" s="24" t="s">
-        <v>441</v>
+        <v>463</v>
       </c>
       <c r="I5" s="24" t="s">
-        <v>442</v>
+        <v>464</v>
       </c>
       <c r="J5" s="24" t="s">
-        <v>443</v>
+        <v>465</v>
       </c>
       <c r="K5" s="24" t="s">
-        <v>444</v>
+        <v>466</v>
       </c>
       <c r="L5" s="24"/>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="25" t="s">
-        <v>438</v>
+        <v>460</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>445</v>
+        <v>467</v>
       </c>
       <c r="C6" s="8" t="str">
         <f aca="false">HYPERLINK("https://codebluecomputing.com","codebluecomputing.com")</f>
         <v>codebluecomputing.com</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>446</v>
+        <v>468</v>
       </c>
       <c r="E6" s="24" t="n">
         <v>2009</v>
       </c>
       <c r="F6" s="23" t="s">
-        <v>447</v>
+        <v>469</v>
       </c>
       <c r="G6" s="23" t="s">
-        <v>448</v>
+        <v>470</v>
       </c>
       <c r="H6" s="24" t="s">
-        <v>449</v>
+        <v>471</v>
       </c>
       <c r="I6" s="24" t="s">
-        <v>450</v>
+        <v>472</v>
       </c>
       <c r="J6" s="24" t="s">
-        <v>451</v>
+        <v>473</v>
       </c>
       <c r="K6" s="24" t="s">
-        <v>452</v>
+        <v>474</v>
       </c>
       <c r="L6" s="24" t="s">
-        <v>453</v>
+        <v>475</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
-        <v>438</v>
+        <v>460</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>454</v>
+        <v>476</v>
       </c>
       <c r="C7" s="8" t="str">
         <f aca="false">HYPERLINK("https://netirio.com","netirio.com")</f>
         <v>netirio.com</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>455</v>
+        <v>477</v>
       </c>
       <c r="E7" s="24" t="n">
         <v>2019</v>
       </c>
       <c r="F7" s="23" t="s">
-        <v>418</v>
+        <v>440</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>456</v>
+        <v>478</v>
       </c>
       <c r="H7" s="24" t="s">
-        <v>457</v>
+        <v>479</v>
       </c>
       <c r="I7" s="24" t="s">
-        <v>458</v>
+        <v>480</v>
       </c>
       <c r="J7" s="24" t="s">
-        <v>459</v>
+        <v>481</v>
       </c>
       <c r="K7" s="24" t="s">
-        <v>460</v>
+        <v>482</v>
       </c>
       <c r="L7" s="24" t="s">
-        <v>461</v>
+        <v>483</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="25" t="s">
-        <v>438</v>
+        <v>460</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>402</v>
+        <v>424</v>
       </c>
       <c r="C8" s="8" t="str">
         <f aca="false">HYPERLINK("https://www.coinfotech.com","www.coinfotech.com")</f>
@@ -7556,34 +8015,34 @@
         <v>92</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>462</v>
+        <v>484</v>
       </c>
       <c r="F8" s="23" t="s">
-        <v>463</v>
+        <v>485</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>464</v>
+        <v>486</v>
       </c>
       <c r="H8" s="24" t="s">
-        <v>404</v>
+        <v>426</v>
       </c>
       <c r="I8" s="24" t="s">
-        <v>465</v>
+        <v>487</v>
       </c>
       <c r="J8" s="24" t="s">
-        <v>466</v>
+        <v>488</v>
       </c>
       <c r="K8" s="24" t="s">
-        <v>467</v>
+        <v>489</v>
       </c>
       <c r="L8" s="24"/>
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="26" t="s">
-        <v>468</v>
+        <v>490</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>469</v>
+        <v>491</v>
       </c>
       <c r="C9" s="8" t="str">
         <f aca="false">HYPERLINK("http://firmaitss.com","firmaitss.com")</f>
@@ -7593,71 +8052,71 @@
         <v>92</v>
       </c>
       <c r="E9" s="24" t="s">
-        <v>470</v>
+        <v>492</v>
       </c>
       <c r="F9" s="23"/>
       <c r="G9" s="23" t="s">
-        <v>471</v>
+        <v>493</v>
       </c>
       <c r="H9" s="24" t="s">
-        <v>472</v>
+        <v>494</v>
       </c>
       <c r="I9" s="24" t="s">
-        <v>473</v>
+        <v>495</v>
       </c>
       <c r="J9" s="24" t="s">
-        <v>474</v>
+        <v>496</v>
       </c>
       <c r="K9" s="24" t="s">
-        <v>475</v>
+        <v>497</v>
       </c>
       <c r="L9" s="24" t="s">
-        <v>476</v>
+        <v>498</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="26" t="s">
-        <v>468</v>
+        <v>490</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>477</v>
+        <v>499</v>
       </c>
       <c r="C10" s="8" t="str">
         <f aca="false">HYPERLINK("https://www.aspiredenver.com","www.aspiredenver.com")</f>
         <v>www.aspiredenver.com</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>478</v>
+        <v>188</v>
       </c>
       <c r="E10" s="24" t="n">
         <v>2000</v>
       </c>
       <c r="F10" s="23" t="s">
-        <v>479</v>
+        <v>500</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>480</v>
+        <v>501</v>
       </c>
       <c r="H10" s="24" t="s">
-        <v>481</v>
+        <v>502</v>
       </c>
       <c r="I10" s="24" t="s">
-        <v>482</v>
+        <v>503</v>
       </c>
       <c r="J10" s="24" t="s">
-        <v>483</v>
+        <v>504</v>
       </c>
       <c r="K10" s="24" t="s">
-        <v>484</v>
+        <v>505</v>
       </c>
       <c r="L10" s="24"/>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="26" t="s">
-        <v>468</v>
+        <v>490</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>485</v>
+        <v>506</v>
       </c>
       <c r="C11" s="8" t="str">
         <f aca="false">HYPERLINK("https://pro-is.com","pro-is.com")</f>
@@ -7670,31 +8129,31 @@
         <v>1998</v>
       </c>
       <c r="F11" s="23" t="s">
-        <v>486</v>
+        <v>507</v>
       </c>
       <c r="G11" s="23" t="s">
-        <v>487</v>
+        <v>508</v>
       </c>
       <c r="H11" s="24" t="s">
-        <v>488</v>
+        <v>509</v>
       </c>
       <c r="I11" s="24" t="s">
-        <v>489</v>
+        <v>510</v>
       </c>
       <c r="J11" s="24" t="s">
-        <v>490</v>
+        <v>511</v>
       </c>
       <c r="K11" s="24" t="s">
-        <v>491</v>
+        <v>512</v>
       </c>
       <c r="L11" s="24"/>
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="26" t="s">
-        <v>468</v>
+        <v>490</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>492</v>
+        <v>513</v>
       </c>
       <c r="C12" s="8" t="str">
         <f aca="false">HYPERLINK("https://northwestdata.com","northwestdata.com")</f>
@@ -7707,68 +8166,68 @@
         <v>1993</v>
       </c>
       <c r="F12" s="23" t="s">
-        <v>479</v>
+        <v>500</v>
       </c>
       <c r="G12" s="23" t="s">
-        <v>493</v>
+        <v>514</v>
       </c>
       <c r="H12" s="24" t="s">
-        <v>494</v>
+        <v>515</v>
       </c>
       <c r="I12" s="24" t="s">
-        <v>495</v>
+        <v>516</v>
       </c>
       <c r="J12" s="24" t="s">
-        <v>496</v>
+        <v>517</v>
       </c>
       <c r="K12" s="24" t="s">
-        <v>497</v>
+        <v>518</v>
       </c>
       <c r="L12" s="24"/>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="26" t="s">
-        <v>468</v>
+        <v>490</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>498</v>
+        <v>519</v>
       </c>
       <c r="C13" s="8" t="str">
         <f aca="false">HYPERLINK("https://www.zentechnologysolutions.com","www.zentechnologysolutions.com")</f>
         <v>www.zentechnologysolutions.com</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>499</v>
+        <v>520</v>
       </c>
       <c r="E13" s="24" t="n">
         <v>2018</v>
       </c>
       <c r="F13" s="23" t="s">
-        <v>500</v>
+        <v>521</v>
       </c>
       <c r="G13" s="23" t="s">
-        <v>501</v>
+        <v>522</v>
       </c>
       <c r="H13" s="24" t="s">
-        <v>502</v>
+        <v>523</v>
       </c>
       <c r="I13" s="24" t="s">
-        <v>503</v>
+        <v>524</v>
       </c>
       <c r="J13" s="24" t="s">
-        <v>504</v>
+        <v>525</v>
       </c>
       <c r="K13" s="24" t="s">
-        <v>505</v>
+        <v>526</v>
       </c>
       <c r="L13" s="24"/>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="26" t="s">
-        <v>468</v>
+        <v>490</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>506</v>
+        <v>527</v>
       </c>
       <c r="C14" s="8" t="str">
         <f aca="false">HYPERLINK("https://c3direct.net","c3direct.net")</f>
@@ -7781,28 +8240,28 @@
         <v>2006</v>
       </c>
       <c r="F14" s="23" t="s">
-        <v>507</v>
+        <v>528</v>
       </c>
       <c r="G14" s="23" t="s">
-        <v>508</v>
+        <v>529</v>
       </c>
       <c r="H14" s="24" t="s">
-        <v>509</v>
+        <v>530</v>
       </c>
       <c r="I14" s="24" t="s">
-        <v>510</v>
+        <v>531</v>
       </c>
       <c r="J14" s="24" t="s">
-        <v>511</v>
+        <v>532</v>
       </c>
       <c r="K14" s="24" t="s">
-        <v>512</v>
+        <v>533</v>
       </c>
       <c r="L14" s="24"/>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="26" t="s">
-        <v>468</v>
+        <v>490</v>
       </c>
       <c r="B15" s="23" t="s">
         <v>67</v>
@@ -7818,354 +8277,354 @@
         <v>2001</v>
       </c>
       <c r="F15" s="23" t="s">
-        <v>513</v>
+        <v>534</v>
       </c>
       <c r="G15" s="23" t="s">
-        <v>514</v>
+        <v>535</v>
       </c>
       <c r="H15" s="24" t="s">
         <v>70</v>
       </c>
       <c r="I15" s="24" t="s">
-        <v>515</v>
+        <v>536</v>
       </c>
       <c r="J15" s="24" t="s">
-        <v>516</v>
+        <v>537</v>
       </c>
       <c r="K15" s="24" t="s">
-        <v>517</v>
+        <v>538</v>
       </c>
       <c r="L15" s="24"/>
     </row>
     <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="26" t="s">
-        <v>468</v>
+        <v>490</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>518</v>
+        <v>539</v>
       </c>
       <c r="C16" s="8" t="str">
         <f aca="false">HYPERLINK("https://wavefinity.net","wavefinity.net")</f>
         <v>wavefinity.net</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>519</v>
+        <v>540</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>520</v>
+        <v>541</v>
       </c>
       <c r="F16" s="23"/>
       <c r="G16" s="23" t="s">
-        <v>521</v>
+        <v>542</v>
       </c>
       <c r="H16" s="24" t="s">
-        <v>522</v>
+        <v>543</v>
       </c>
       <c r="I16" s="24" t="s">
-        <v>523</v>
+        <v>544</v>
       </c>
       <c r="J16" s="24" t="s">
-        <v>524</v>
+        <v>545</v>
       </c>
       <c r="K16" s="24" t="s">
-        <v>525</v>
+        <v>546</v>
       </c>
       <c r="L16" s="24"/>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="26" t="s">
-        <v>468</v>
+        <v>490</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>526</v>
+        <v>547</v>
       </c>
       <c r="C17" s="23"/>
       <c r="D17" s="23" t="s">
-        <v>527</v>
+        <v>548</v>
       </c>
       <c r="E17" s="24" t="s">
-        <v>528</v>
+        <v>549</v>
       </c>
       <c r="F17" s="27" t="n">
         <v>2001</v>
       </c>
       <c r="G17" s="23" t="s">
-        <v>529</v>
+        <v>550</v>
       </c>
       <c r="H17" s="24" t="s">
-        <v>530</v>
+        <v>551</v>
       </c>
       <c r="I17" s="24" t="s">
-        <v>531</v>
+        <v>552</v>
       </c>
       <c r="J17" s="24" t="s">
-        <v>532</v>
+        <v>553</v>
       </c>
       <c r="K17" s="24" t="s">
-        <v>533</v>
+        <v>554</v>
       </c>
       <c r="L17" s="24"/>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="26" t="s">
-        <v>468</v>
+        <v>490</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>534</v>
+        <v>555</v>
       </c>
       <c r="C18" s="8" t="str">
         <f aca="false">HYPERLINK("https://www.entechitsolutions.com","www.entechitsolutions.com")</f>
         <v>www.entechitsolutions.com</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>535</v>
+        <v>556</v>
       </c>
       <c r="E18" s="24" t="n">
         <v>2010</v>
       </c>
       <c r="F18" s="23" t="s">
-        <v>536</v>
+        <v>557</v>
       </c>
       <c r="G18" s="23" t="s">
-        <v>537</v>
+        <v>558</v>
       </c>
       <c r="H18" s="24" t="s">
-        <v>538</v>
+        <v>559</v>
       </c>
       <c r="I18" s="24" t="s">
-        <v>539</v>
+        <v>560</v>
       </c>
       <c r="J18" s="24" t="s">
-        <v>540</v>
+        <v>561</v>
       </c>
       <c r="K18" s="24" t="s">
-        <v>541</v>
+        <v>562</v>
       </c>
       <c r="L18" s="24" t="s">
-        <v>542</v>
+        <v>563</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="26" t="s">
-        <v>468</v>
+        <v>490</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>543</v>
+        <v>564</v>
       </c>
       <c r="C19" s="8" t="str">
         <f aca="false">HYPERLINK("https://imperitiv.com","imperitiv.com")</f>
         <v>imperitiv.com</v>
       </c>
       <c r="D19" s="23" t="s">
-        <v>544</v>
+        <v>565</v>
       </c>
       <c r="E19" s="24" t="n">
         <v>2015</v>
       </c>
       <c r="F19" s="23" t="s">
-        <v>536</v>
+        <v>557</v>
       </c>
       <c r="G19" s="23" t="s">
-        <v>545</v>
+        <v>566</v>
       </c>
       <c r="H19" s="24" t="s">
-        <v>546</v>
+        <v>567</v>
       </c>
       <c r="I19" s="24" t="s">
-        <v>547</v>
+        <v>568</v>
       </c>
       <c r="J19" s="24" t="s">
-        <v>548</v>
+        <v>569</v>
       </c>
       <c r="K19" s="24" t="s">
-        <v>549</v>
+        <v>570</v>
       </c>
       <c r="L19" s="24" t="s">
-        <v>550</v>
+        <v>571</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="26" t="s">
-        <v>468</v>
+        <v>490</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>551</v>
+        <v>572</v>
       </c>
       <c r="C20" s="8" t="str">
         <f aca="false">HYPERLINK("https://www.pr272managedit.com","www.pr272managedit.com")</f>
         <v>www.pr272managedit.com</v>
       </c>
       <c r="D20" s="23" t="s">
-        <v>552</v>
+        <v>573</v>
       </c>
       <c r="E20" s="24" t="s">
-        <v>553</v>
+        <v>574</v>
       </c>
       <c r="F20" s="23" t="s">
-        <v>486</v>
+        <v>507</v>
       </c>
       <c r="G20" s="23" t="s">
-        <v>554</v>
+        <v>575</v>
       </c>
       <c r="H20" s="24" t="s">
-        <v>555</v>
+        <v>576</v>
       </c>
       <c r="I20" s="24" t="s">
-        <v>556</v>
+        <v>577</v>
       </c>
       <c r="J20" s="24" t="s">
-        <v>557</v>
+        <v>578</v>
       </c>
       <c r="K20" s="24" t="s">
-        <v>558</v>
+        <v>579</v>
       </c>
       <c r="L20" s="24"/>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="26" t="s">
-        <v>468</v>
+        <v>490</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>559</v>
+        <v>580</v>
       </c>
       <c r="C21" s="8" t="str">
         <f aca="false">HYPERLINK("https://computerservicebreckenridge.com","computerservicebreckenridge.com")</f>
         <v>computerservicebreckenridge.com</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>560</v>
+        <v>581</v>
       </c>
       <c r="E21" s="24" t="n">
         <v>2001</v>
       </c>
       <c r="F21" s="23" t="s">
-        <v>561</v>
+        <v>582</v>
       </c>
       <c r="G21" s="23" t="s">
-        <v>562</v>
+        <v>583</v>
       </c>
       <c r="H21" s="24" t="s">
-        <v>563</v>
+        <v>584</v>
       </c>
       <c r="I21" s="24" t="s">
-        <v>564</v>
+        <v>585</v>
       </c>
       <c r="J21" s="24" t="s">
-        <v>565</v>
+        <v>586</v>
       </c>
       <c r="K21" s="24" t="s">
-        <v>566</v>
+        <v>587</v>
       </c>
       <c r="L21" s="24"/>
     </row>
     <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="26" t="s">
-        <v>468</v>
+        <v>490</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>567</v>
+        <v>588</v>
       </c>
       <c r="C22" s="8" t="str">
         <f aca="false">HYPERLINK("https://rfhelpdesk.net","rfhelpdesk.net")</f>
         <v>rfhelpdesk.net</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>568</v>
+        <v>589</v>
       </c>
       <c r="E22" s="24" t="s">
-        <v>569</v>
+        <v>590</v>
       </c>
       <c r="F22" s="23" t="s">
-        <v>486</v>
+        <v>507</v>
       </c>
       <c r="G22" s="23" t="s">
-        <v>570</v>
+        <v>591</v>
       </c>
       <c r="H22" s="24" t="s">
-        <v>571</v>
+        <v>592</v>
       </c>
       <c r="I22" s="24" t="s">
-        <v>572</v>
+        <v>593</v>
       </c>
       <c r="J22" s="24" t="s">
-        <v>573</v>
+        <v>594</v>
       </c>
       <c r="K22" s="24" t="s">
-        <v>574</v>
+        <v>595</v>
       </c>
       <c r="L22" s="24"/>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="26" t="s">
-        <v>468</v>
+        <v>490</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>575</v>
+        <v>596</v>
       </c>
       <c r="C23" s="8" t="str">
         <f aca="false">HYPERLINK("https://olive.tech","olive.tech")</f>
         <v>olive.tech</v>
       </c>
       <c r="D23" s="23" t="s">
-        <v>576</v>
+        <v>597</v>
       </c>
       <c r="E23" s="24" t="n">
         <v>2021</v>
       </c>
       <c r="F23" s="23" t="s">
-        <v>577</v>
+        <v>598</v>
       </c>
       <c r="G23" s="23" t="s">
-        <v>578</v>
+        <v>599</v>
       </c>
       <c r="H23" s="24" t="s">
-        <v>579</v>
+        <v>600</v>
       </c>
       <c r="I23" s="24" t="s">
-        <v>580</v>
+        <v>601</v>
       </c>
       <c r="J23" s="24" t="s">
-        <v>581</v>
+        <v>602</v>
       </c>
       <c r="K23" s="24" t="s">
-        <v>582</v>
+        <v>603</v>
       </c>
       <c r="L23" s="24"/>
     </row>
     <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="28" t="s">
-        <v>583</v>
+        <v>604</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>276</v>
+        <v>298</v>
       </c>
       <c r="C24" s="8" t="str">
         <f aca="false">HYPERLINK("https://www.trioptech.com","www.trioptech.com")</f>
         <v>www.trioptech.com</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>277</v>
+        <v>299</v>
       </c>
       <c r="E24" s="24" t="s">
-        <v>584</v>
+        <v>605</v>
       </c>
       <c r="F24" s="27" t="n">
         <v>2020</v>
       </c>
       <c r="G24" s="23" t="s">
-        <v>585</v>
+        <v>606</v>
       </c>
       <c r="H24" s="24" t="s">
-        <v>586</v>
+        <v>607</v>
       </c>
       <c r="I24" s="24" t="s">
-        <v>587</v>
+        <v>608</v>
       </c>
       <c r="J24" s="24" t="s">
-        <v>588</v>
+        <v>609</v>
       </c>
       <c r="K24" s="24" t="s">
-        <v>589</v>
+        <v>610</v>
       </c>
       <c r="L24" s="24"/>
     </row>
@@ -8174,7 +8633,7 @@
         <v>125</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>590</v>
+        <v>611</v>
       </c>
       <c r="C25" s="8" t="str">
         <f aca="false">HYPERLINK("https://www.ramdyne.com","www.ramdyne.com")</f>
@@ -8187,22 +8646,22 @@
         <v>2007</v>
       </c>
       <c r="F25" s="23" t="s">
-        <v>591</v>
+        <v>612</v>
       </c>
       <c r="G25" s="23" t="s">
-        <v>592</v>
+        <v>613</v>
       </c>
       <c r="H25" s="24" t="s">
-        <v>593</v>
+        <v>614</v>
       </c>
       <c r="I25" s="24" t="s">
-        <v>594</v>
+        <v>615</v>
       </c>
       <c r="J25" s="24" t="s">
-        <v>595</v>
+        <v>616</v>
       </c>
       <c r="K25" s="24" t="s">
-        <v>596</v>
+        <v>617</v>
       </c>
       <c r="L25" s="24"/>
     </row>
@@ -8211,7 +8670,7 @@
         <v>125</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>597</v>
+        <v>618</v>
       </c>
       <c r="C26" s="8" t="str">
         <f aca="false">HYPERLINK("https://integtech.net","integtech.net")</f>
@@ -8224,22 +8683,22 @@
         <v>2016</v>
       </c>
       <c r="F26" s="23" t="s">
-        <v>486</v>
+        <v>507</v>
       </c>
       <c r="G26" s="23" t="s">
-        <v>598</v>
+        <v>619</v>
       </c>
       <c r="H26" s="24" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="I26" s="24" t="s">
-        <v>599</v>
+        <v>620</v>
       </c>
       <c r="J26" s="24" t="s">
-        <v>600</v>
+        <v>621</v>
       </c>
       <c r="K26" s="24" t="s">
-        <v>601</v>
+        <v>622</v>
       </c>
       <c r="L26" s="24"/>
     </row>
@@ -8248,35 +8707,35 @@
         <v>125</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>602</v>
+        <v>623</v>
       </c>
       <c r="C27" s="8" t="str">
         <f aca="false">HYPERLINK("https://mdlconsultinginc.net","mdlconsultinginc.net")</f>
         <v>mdlconsultinginc.net</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>603</v>
+        <v>624</v>
       </c>
       <c r="E27" s="24" t="n">
         <v>2001</v>
       </c>
       <c r="F27" s="23" t="s">
-        <v>604</v>
+        <v>625</v>
       </c>
       <c r="G27" s="23" t="s">
-        <v>605</v>
+        <v>626</v>
       </c>
       <c r="H27" s="24" t="s">
-        <v>606</v>
+        <v>627</v>
       </c>
       <c r="I27" s="24" t="s">
-        <v>607</v>
+        <v>628</v>
       </c>
       <c r="J27" s="24" t="s">
-        <v>608</v>
+        <v>629</v>
       </c>
       <c r="K27" s="24" t="s">
-        <v>609</v>
+        <v>630</v>
       </c>
       <c r="L27" s="24"/>
     </row>
@@ -8285,35 +8744,35 @@
         <v>125</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>610</v>
+        <v>631</v>
       </c>
       <c r="C28" s="8" t="str">
         <f aca="false">HYPERLINK("https://coloradocomputers.net","coloradocomputers.net")</f>
         <v>coloradocomputers.net</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>611</v>
+        <v>632</v>
       </c>
       <c r="E28" s="24" t="n">
         <v>1997</v>
       </c>
       <c r="F28" s="23" t="s">
-        <v>612</v>
+        <v>633</v>
       </c>
       <c r="G28" s="23" t="s">
-        <v>613</v>
+        <v>634</v>
       </c>
       <c r="H28" s="24" t="s">
-        <v>614</v>
+        <v>635</v>
       </c>
       <c r="I28" s="24" t="s">
-        <v>615</v>
+        <v>636</v>
       </c>
       <c r="J28" s="24" t="s">
-        <v>616</v>
+        <v>637</v>
       </c>
       <c r="K28" s="24" t="s">
-        <v>617</v>
+        <v>638</v>
       </c>
       <c r="L28" s="24"/>
     </row>
@@ -8322,35 +8781,35 @@
         <v>125</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>618</v>
+        <v>639</v>
       </c>
       <c r="C29" s="8" t="str">
         <f aca="false">HYPERLINK("https://www.simplytechdenver.com","www.simplytechdenver.com")</f>
         <v>www.simplytechdenver.com</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>619</v>
+        <v>640</v>
       </c>
       <c r="E29" s="24" t="n">
         <v>2017</v>
       </c>
       <c r="F29" s="23" t="s">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="G29" s="23" t="s">
-        <v>621</v>
+        <v>642</v>
       </c>
       <c r="H29" s="24" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="I29" s="24" t="s">
-        <v>622</v>
+        <v>643</v>
       </c>
       <c r="J29" s="24" t="s">
-        <v>623</v>
+        <v>644</v>
       </c>
       <c r="K29" s="24" t="s">
-        <v>624</v>
+        <v>645</v>
       </c>
       <c r="L29" s="24"/>
     </row>
@@ -8359,7 +8818,7 @@
         <v>125</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>625</v>
+        <v>646</v>
       </c>
       <c r="C30" s="8" t="str">
         <f aca="false">HYPERLINK("https://mycoloradocomputerguy.com","mycoloradocomputerguy.com")</f>
@@ -8372,47 +8831,201 @@
         <v>2010</v>
       </c>
       <c r="F30" s="23" t="s">
-        <v>626</v>
+        <v>647</v>
       </c>
       <c r="G30" s="23" t="s">
-        <v>627</v>
+        <v>648</v>
       </c>
       <c r="H30" s="24" t="s">
-        <v>628</v>
+        <v>649</v>
       </c>
       <c r="I30" s="24" t="s">
-        <v>629</v>
+        <v>650</v>
       </c>
       <c r="J30" s="24" t="s">
-        <v>630</v>
+        <v>651</v>
       </c>
       <c r="K30" s="24" t="s">
-        <v>631</v>
+        <v>652</v>
       </c>
       <c r="L30" s="24"/>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="30" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="31" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="31" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="32" t="s">
-        <v>635</v>
+    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="26" t="s">
+        <v>490</v>
+      </c>
+      <c r="B31" s="23" t="s">
+        <v>653</v>
+      </c>
+      <c r="C31" s="8" t="str">
+        <f aca="false">HYPERLINK("https://speedwise.net","speedwise.net")</f>
+        <v>speedwise.net</v>
+      </c>
+      <c r="D31" s="23" t="s">
+        <v>654</v>
+      </c>
+      <c r="E31" s="24" t="n">
+        <v>2004</v>
+      </c>
+      <c r="F31" s="23" t="s">
+        <v>655</v>
+      </c>
+      <c r="G31" s="23" t="s">
+        <v>656</v>
+      </c>
+      <c r="H31" s="24" t="s">
+        <v>657</v>
+      </c>
+      <c r="I31" s="24" t="s">
+        <v>658</v>
+      </c>
+      <c r="J31" s="24" t="s">
+        <v>659</v>
+      </c>
+      <c r="K31" s="24" t="s">
+        <v>660</v>
+      </c>
+      <c r="L31" s="24" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="26" t="s">
+        <v>490</v>
+      </c>
+      <c r="B32" s="23" t="s">
+        <v>662</v>
+      </c>
+      <c r="C32" s="8" t="str">
+        <f aca="false">HYPERLINK("https://thinkwaypoint.com","thinkwaypoint.com")</f>
+        <v>thinkwaypoint.com</v>
+      </c>
+      <c r="D32" s="23" t="s">
+        <v>663</v>
+      </c>
+      <c r="E32" s="24" t="n">
+        <v>2011</v>
+      </c>
+      <c r="F32" s="23" t="s">
+        <v>664</v>
+      </c>
+      <c r="G32" s="23" t="s">
+        <v>665</v>
+      </c>
+      <c r="H32" s="24" t="s">
+        <v>666</v>
+      </c>
+      <c r="I32" s="24" t="s">
+        <v>667</v>
+      </c>
+      <c r="J32" s="24" t="s">
+        <v>668</v>
+      </c>
+      <c r="K32" s="24" t="s">
+        <v>669</v>
+      </c>
+      <c r="L32" s="24" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="28" t="s">
+        <v>604</v>
+      </c>
+      <c r="B33" s="23" t="s">
+        <v>671</v>
+      </c>
+      <c r="C33" s="8" t="str">
+        <f aca="false">HYPERLINK("https://mynewitguys.com","mynewitguys.com")</f>
+        <v>mynewitguys.com</v>
+      </c>
+      <c r="D33" s="23" t="s">
+        <v>672</v>
+      </c>
+      <c r="E33" s="24" t="n">
+        <v>2009</v>
+      </c>
+      <c r="F33" s="23" t="s">
+        <v>673</v>
+      </c>
+      <c r="G33" s="23" t="s">
+        <v>674</v>
+      </c>
+      <c r="H33" s="24" t="s">
+        <v>666</v>
+      </c>
+      <c r="I33" s="24" t="s">
+        <v>675</v>
+      </c>
+      <c r="J33" s="24" t="s">
+        <v>676</v>
+      </c>
+      <c r="K33" s="24" t="s">
+        <v>677</v>
+      </c>
+      <c r="L33" s="24"/>
+    </row>
+    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="28" t="s">
+        <v>604</v>
+      </c>
+      <c r="B34" s="23" t="s">
+        <v>678</v>
+      </c>
+      <c r="C34" s="8" t="str">
+        <f aca="false">HYPERLINK("https://workplaceit.net","workplaceit.net")</f>
+        <v>workplaceit.net</v>
+      </c>
+      <c r="D34" s="23" t="s">
+        <v>679</v>
+      </c>
+      <c r="E34" s="24" t="n">
+        <v>2016</v>
+      </c>
+      <c r="F34" s="23" t="s">
+        <v>680</v>
+      </c>
+      <c r="G34" s="23" t="s">
+        <v>681</v>
+      </c>
+      <c r="H34" s="24" t="s">
+        <v>682</v>
+      </c>
+      <c r="I34" s="24" t="s">
+        <v>683</v>
+      </c>
+      <c r="J34" s="24" t="s">
+        <v>684</v>
+      </c>
+      <c r="K34" s="24" t="s">
+        <v>685</v>
+      </c>
+      <c r="L34" s="24" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="30" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="31" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="31" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="32" t="s">
+        <v>690</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L30"/>
+  <autoFilter ref="A1:L34"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -8445,626 +9058,626 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>636</v>
+        <v>691</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>637</v>
+        <v>692</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>638</v>
+        <v>693</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>639</v>
+        <v>694</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>640</v>
+        <v>695</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>641</v>
+        <v>696</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>642</v>
+        <v>697</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>643</v>
+        <v>698</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="33" t="s">
-        <v>644</v>
+        <v>699</v>
       </c>
       <c r="B2" s="33" t="s">
-        <v>645</v>
+        <v>700</v>
       </c>
       <c r="C2" s="13" t="str">
         <f aca="false">HYPERLINK("https://www.newchartertech.com","www.newchartertech.com")</f>
         <v>www.newchartertech.com</v>
       </c>
       <c r="D2" s="34" t="s">
-        <v>646</v>
+        <v>701</v>
       </c>
       <c r="E2" s="34" t="s">
-        <v>647</v>
+        <v>702</v>
       </c>
       <c r="F2" s="34" t="s">
-        <v>648</v>
+        <v>703</v>
       </c>
       <c r="G2" s="34" t="s">
-        <v>649</v>
+        <v>704</v>
       </c>
       <c r="H2" s="34" t="s">
-        <v>650</v>
+        <v>705</v>
       </c>
       <c r="I2" s="34" t="s">
-        <v>651</v>
+        <v>706</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="33" t="s">
-        <v>652</v>
+        <v>707</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>653</v>
+        <v>708</v>
       </c>
       <c r="C3" s="13" t="str">
         <f aca="false">HYPERLINK("https://www.dataprise.com","www.dataprise.com")</f>
         <v>www.dataprise.com</v>
       </c>
       <c r="D3" s="34" t="s">
-        <v>654</v>
+        <v>709</v>
       </c>
       <c r="E3" s="34" t="s">
-        <v>655</v>
+        <v>710</v>
       </c>
       <c r="F3" s="34" t="s">
-        <v>656</v>
+        <v>711</v>
       </c>
       <c r="G3" s="34" t="s">
-        <v>657</v>
+        <v>712</v>
       </c>
       <c r="H3" s="34" t="s">
-        <v>658</v>
+        <v>713</v>
       </c>
       <c r="I3" s="34" t="s">
-        <v>659</v>
+        <v>714</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="33" t="s">
-        <v>660</v>
+        <v>715</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>661</v>
+        <v>716</v>
       </c>
       <c r="C4" s="13" t="str">
         <f aca="false">HYPERLINK("https://www.ntiva.com","www.ntiva.com")</f>
         <v>www.ntiva.com</v>
       </c>
       <c r="D4" s="34" t="s">
-        <v>654</v>
+        <v>709</v>
       </c>
       <c r="E4" s="34" t="s">
-        <v>662</v>
+        <v>717</v>
       </c>
       <c r="F4" s="34" t="s">
-        <v>663</v>
+        <v>718</v>
       </c>
       <c r="G4" s="34" t="s">
-        <v>664</v>
+        <v>719</v>
       </c>
       <c r="H4" s="34" t="s">
-        <v>665</v>
+        <v>720</v>
       </c>
       <c r="I4" s="34" t="s">
-        <v>666</v>
+        <v>721</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="33" t="s">
-        <v>667</v>
+        <v>722</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>668</v>
+        <v>723</v>
       </c>
       <c r="C5" s="13" t="str">
         <f aca="false">HYPERLINK("https://meriplex.com","meriplex.com")</f>
         <v>meriplex.com</v>
       </c>
       <c r="D5" s="34" t="s">
-        <v>654</v>
+        <v>709</v>
       </c>
       <c r="E5" s="34" t="s">
-        <v>669</v>
+        <v>724</v>
       </c>
       <c r="F5" s="34" t="s">
-        <v>670</v>
+        <v>725</v>
       </c>
       <c r="G5" s="34" t="s">
-        <v>671</v>
+        <v>726</v>
       </c>
       <c r="H5" s="34" t="s">
-        <v>672</v>
+        <v>727</v>
       </c>
       <c r="I5" s="34" t="s">
-        <v>673</v>
+        <v>728</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="33" t="s">
-        <v>674</v>
+        <v>729</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>675</v>
+        <v>730</v>
       </c>
       <c r="C6" s="13" t="str">
         <f aca="false">HYPERLINK("https://www.appliedtech.us","www.appliedtech.us")</f>
         <v>www.appliedtech.us</v>
       </c>
       <c r="D6" s="34" t="s">
-        <v>676</v>
+        <v>731</v>
       </c>
       <c r="E6" s="34" t="s">
-        <v>677</v>
+        <v>732</v>
       </c>
       <c r="F6" s="34" t="s">
-        <v>678</v>
+        <v>733</v>
       </c>
       <c r="G6" s="34" t="s">
-        <v>367</v>
+        <v>389</v>
       </c>
       <c r="H6" s="34" t="s">
-        <v>679</v>
+        <v>734</v>
       </c>
       <c r="I6" s="34" t="s">
-        <v>680</v>
+        <v>735</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="33" t="s">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>681</v>
+        <v>736</v>
       </c>
       <c r="C7" s="13" t="str">
         <f aca="false">HYPERLINK("https://www.nexustek.com","www.nexustek.com")</f>
         <v>www.nexustek.com</v>
       </c>
       <c r="D7" s="34" t="s">
-        <v>654</v>
+        <v>709</v>
       </c>
       <c r="E7" s="34" t="s">
-        <v>682</v>
+        <v>737</v>
       </c>
       <c r="F7" s="34" t="s">
-        <v>683</v>
+        <v>738</v>
       </c>
       <c r="G7" s="34" t="s">
-        <v>684</v>
+        <v>739</v>
       </c>
       <c r="H7" s="34" t="s">
-        <v>685</v>
+        <v>740</v>
       </c>
       <c r="I7" s="34" t="s">
-        <v>686</v>
+        <v>741</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="33" t="s">
-        <v>687</v>
+        <v>742</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>688</v>
+        <v>743</v>
       </c>
       <c r="C8" s="13" t="str">
         <f aca="false">HYPERLINK("https://harborit.com","harborit.com")</f>
         <v>harborit.com</v>
       </c>
       <c r="D8" s="34" t="s">
-        <v>689</v>
+        <v>744</v>
       </c>
       <c r="E8" s="34" t="s">
-        <v>690</v>
+        <v>745</v>
       </c>
       <c r="F8" s="34" t="s">
-        <v>691</v>
+        <v>746</v>
       </c>
       <c r="G8" s="34" t="s">
-        <v>692</v>
+        <v>747</v>
       </c>
       <c r="H8" s="34" t="s">
-        <v>693</v>
+        <v>748</v>
       </c>
       <c r="I8" s="34" t="s">
-        <v>694</v>
+        <v>749</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="33" t="s">
-        <v>695</v>
+        <v>750</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>696</v>
+        <v>751</v>
       </c>
       <c r="C9" s="13" t="str">
         <f aca="false">HYPERLINK("https://www.sourcepass.com","www.sourcepass.com")</f>
         <v>www.sourcepass.com</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>697</v>
+        <v>752</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>698</v>
+        <v>753</v>
       </c>
       <c r="F9" s="34" t="s">
-        <v>699</v>
+        <v>754</v>
       </c>
       <c r="G9" s="34" t="s">
-        <v>700</v>
+        <v>755</v>
       </c>
       <c r="H9" s="34" t="s">
-        <v>701</v>
+        <v>756</v>
       </c>
       <c r="I9" s="34" t="s">
-        <v>673</v>
+        <v>728</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="33" t="s">
-        <v>702</v>
+        <v>757</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>703</v>
+        <v>758</v>
       </c>
       <c r="C10" s="13" t="str">
         <f aca="false">HYPERLINK("https://integrisit.com","integrisit.com")</f>
         <v>integrisit.com</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>654</v>
+        <v>709</v>
       </c>
       <c r="E10" s="34" t="s">
-        <v>704</v>
+        <v>759</v>
       </c>
       <c r="F10" s="34" t="s">
-        <v>705</v>
+        <v>760</v>
       </c>
       <c r="G10" s="34" t="s">
-        <v>706</v>
+        <v>761</v>
       </c>
       <c r="H10" s="34" t="s">
-        <v>707</v>
+        <v>762</v>
       </c>
       <c r="I10" s="34" t="s">
-        <v>673</v>
+        <v>728</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="33" t="s">
-        <v>708</v>
+        <v>763</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>668</v>
+        <v>723</v>
       </c>
       <c r="C11" s="13" t="str">
         <f aca="false">HYPERLINK("https://www.ironedgegroup.com","www.ironedgegroup.com")</f>
         <v>www.ironedgegroup.com</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>654</v>
+        <v>709</v>
       </c>
       <c r="E11" s="34" t="s">
-        <v>709</v>
+        <v>764</v>
       </c>
       <c r="F11" s="34" t="s">
-        <v>710</v>
+        <v>765</v>
       </c>
       <c r="G11" s="34" t="s">
-        <v>351</v>
+        <v>373</v>
       </c>
       <c r="H11" s="34" t="s">
-        <v>711</v>
+        <v>766</v>
       </c>
       <c r="I11" s="34" t="s">
-        <v>673</v>
+        <v>728</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="33" t="s">
-        <v>712</v>
+        <v>767</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>713</v>
+        <v>768</v>
       </c>
       <c r="C12" s="13" t="str">
         <f aca="false">HYPERLINK("https://vertilocity.com","vertilocity.com")</f>
         <v>vertilocity.com</v>
       </c>
       <c r="D12" s="34" t="s">
-        <v>714</v>
+        <v>769</v>
       </c>
       <c r="E12" s="34" t="s">
-        <v>715</v>
+        <v>770</v>
       </c>
       <c r="F12" s="34" t="s">
-        <v>716</v>
+        <v>771</v>
       </c>
       <c r="G12" s="34" t="s">
-        <v>717</v>
+        <v>772</v>
       </c>
       <c r="H12" s="34" t="s">
-        <v>718</v>
+        <v>773</v>
       </c>
       <c r="I12" s="34" t="s">
-        <v>719</v>
+        <v>774</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="33" t="s">
-        <v>720</v>
+        <v>775</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>721</v>
+        <v>776</v>
       </c>
       <c r="C13" s="13" t="str">
         <f aca="false">HYPERLINK("https://trace3.com","trace3.com")</f>
         <v>trace3.com</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>722</v>
+        <v>777</v>
       </c>
       <c r="E13" s="34" t="s">
-        <v>723</v>
+        <v>778</v>
       </c>
       <c r="F13" s="34" t="s">
-        <v>724</v>
+        <v>779</v>
       </c>
       <c r="G13" s="34" t="s">
-        <v>725</v>
+        <v>780</v>
       </c>
       <c r="H13" s="34" t="s">
-        <v>726</v>
+        <v>781</v>
       </c>
       <c r="I13" s="34" t="s">
-        <v>727</v>
+        <v>782</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="33" t="s">
-        <v>728</v>
+        <v>783</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>729</v>
+        <v>784</v>
       </c>
       <c r="C14" s="13" t="str">
         <f aca="false">HYPERLINK("","")</f>
         <v/>
       </c>
       <c r="D14" s="34" t="s">
-        <v>730</v>
+        <v>785</v>
       </c>
       <c r="E14" s="34" t="s">
-        <v>731</v>
+        <v>786</v>
       </c>
       <c r="F14" s="34" t="s">
-        <v>732</v>
+        <v>787</v>
       </c>
       <c r="G14" s="34" t="s">
-        <v>733</v>
+        <v>788</v>
       </c>
       <c r="H14" s="34" t="s">
-        <v>734</v>
+        <v>789</v>
       </c>
       <c r="I14" s="34" t="s">
-        <v>735</v>
+        <v>790</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="33" t="s">
-        <v>736</v>
+        <v>791</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>737</v>
+        <v>792</v>
       </c>
       <c r="C15" s="13" t="str">
         <f aca="false">HYPERLINK("https://networksunlimited.com","networksunlimited.com")</f>
         <v>networksunlimited.com</v>
       </c>
       <c r="D15" s="34" t="s">
-        <v>738</v>
+        <v>793</v>
       </c>
       <c r="E15" s="34" t="s">
-        <v>739</v>
+        <v>794</v>
       </c>
       <c r="F15" s="34" t="s">
-        <v>740</v>
+        <v>795</v>
       </c>
       <c r="G15" s="34" t="s">
-        <v>741</v>
+        <v>796</v>
       </c>
       <c r="H15" s="34" t="s">
-        <v>742</v>
+        <v>797</v>
       </c>
       <c r="I15" s="34" t="s">
-        <v>743</v>
+        <v>798</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="33" t="s">
-        <v>744</v>
+        <v>799</v>
       </c>
       <c r="B16" s="33" t="s">
-        <v>745</v>
+        <v>800</v>
       </c>
       <c r="C16" s="13" t="str">
         <f aca="false">HYPERLINK("https://www.evergreensg.com","www.evergreensg.com")</f>
         <v>www.evergreensg.com</v>
       </c>
       <c r="D16" s="34" t="s">
-        <v>746</v>
+        <v>801</v>
       </c>
       <c r="E16" s="34" t="s">
-        <v>747</v>
+        <v>802</v>
       </c>
       <c r="F16" s="34" t="s">
-        <v>748</v>
+        <v>803</v>
       </c>
       <c r="G16" s="34" t="s">
-        <v>749</v>
+        <v>804</v>
       </c>
       <c r="H16" s="34" t="s">
-        <v>750</v>
+        <v>805</v>
       </c>
       <c r="I16" s="34" t="s">
-        <v>751</v>
+        <v>806</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="33" t="s">
-        <v>752</v>
+        <v>807</v>
       </c>
       <c r="B17" s="33" t="s">
-        <v>753</v>
+        <v>808</v>
       </c>
       <c r="C17" s="13" t="str">
         <f aca="false">HYPERLINK("https://www.the20msp.com","www.the20msp.com")</f>
         <v>www.the20msp.com</v>
       </c>
       <c r="D17" s="34" t="s">
-        <v>754</v>
+        <v>809</v>
       </c>
       <c r="E17" s="34" t="s">
-        <v>755</v>
+        <v>810</v>
       </c>
       <c r="F17" s="34" t="s">
-        <v>756</v>
+        <v>811</v>
       </c>
       <c r="G17" s="34" t="s">
-        <v>757</v>
+        <v>812</v>
       </c>
       <c r="H17" s="34" t="s">
-        <v>758</v>
+        <v>813</v>
       </c>
       <c r="I17" s="34" t="s">
-        <v>759</v>
+        <v>814</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="23" t="s">
-        <v>760</v>
+        <v>815</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>761</v>
+        <v>816</v>
       </c>
       <c r="C18" s="8" t="str">
         <f aca="false">HYPERLINK("https://thrivenextgen.com","thrivenextgen.com")</f>
         <v>thrivenextgen.com</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>654</v>
+        <v>709</v>
       </c>
       <c r="E18" s="24" t="s">
-        <v>762</v>
+        <v>817</v>
       </c>
       <c r="F18" s="24" t="s">
-        <v>763</v>
+        <v>818</v>
       </c>
       <c r="G18" s="24" t="s">
-        <v>764</v>
+        <v>819</v>
       </c>
       <c r="H18" s="24" t="s">
-        <v>765</v>
+        <v>820</v>
       </c>
       <c r="I18" s="24" t="s">
-        <v>766</v>
+        <v>821</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="23" t="s">
-        <v>767</v>
+        <v>822</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>768</v>
+        <v>823</v>
       </c>
       <c r="C19" s="8" t="str">
         <f aca="false">HYPERLINK("https://corsicatech.com","corsicatech.com")</f>
         <v>corsicatech.com</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>769</v>
+        <v>824</v>
       </c>
       <c r="E19" s="24" t="s">
-        <v>770</v>
+        <v>825</v>
       </c>
       <c r="F19" s="24" t="s">
-        <v>771</v>
+        <v>826</v>
       </c>
       <c r="G19" s="24" t="s">
-        <v>772</v>
+        <v>827</v>
       </c>
       <c r="H19" s="24" t="s">
-        <v>773</v>
+        <v>828</v>
       </c>
       <c r="I19" s="24" t="s">
-        <v>766</v>
+        <v>821</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="33" t="s">
-        <v>774</v>
+        <v>829</v>
       </c>
       <c r="B20" s="33" t="s">
-        <v>775</v>
+        <v>830</v>
       </c>
       <c r="C20" s="13" t="str">
         <f aca="false">HYPERLINK("","")</f>
         <v/>
       </c>
       <c r="D20" s="34" t="s">
-        <v>776</v>
+        <v>831</v>
       </c>
       <c r="E20" s="34" t="s">
-        <v>777</v>
+        <v>832</v>
       </c>
       <c r="F20" s="34" t="s">
-        <v>778</v>
+        <v>833</v>
       </c>
       <c r="G20" s="34" t="s">
-        <v>779</v>
+        <v>834</v>
       </c>
       <c r="H20" s="34" t="s">
-        <v>780</v>
+        <v>835</v>
       </c>
       <c r="I20" s="34" t="s">
-        <v>781</v>
+        <v>836</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="35" t="s">
-        <v>782</v>
+        <v>837</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="36" t="s">
-        <v>783</v>
+        <v>838</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="36" t="s">
-        <v>784</v>
+        <v>839</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="36" t="s">
-        <v>785</v>
+        <v>840</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="36" t="s">
-        <v>786</v>
+        <v>841</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9072,7 +9685,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="35" t="s">
-        <v>787</v>
+        <v>842</v>
       </c>
     </row>
   </sheetData>
@@ -9093,7 +9706,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38"/>
@@ -9108,59 +9721,59 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="37" t="s">
-        <v>788</v>
+        <v>843</v>
       </c>
       <c r="B1" s="37" t="s">
-        <v>637</v>
+        <v>692</v>
       </c>
       <c r="C1" s="37" t="s">
         <v>4</v>
       </c>
       <c r="D1" s="37" t="s">
-        <v>789</v>
+        <v>844</v>
       </c>
       <c r="E1" s="37" t="s">
-        <v>790</v>
+        <v>845</v>
       </c>
       <c r="F1" s="37" t="s">
-        <v>791</v>
+        <v>846</v>
       </c>
       <c r="G1" s="37" t="s">
-        <v>792</v>
+        <v>847</v>
       </c>
       <c r="H1" s="37" t="s">
-        <v>793</v>
+        <v>848</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="24" t="s">
-        <v>352</v>
+        <v>374</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>353</v>
+        <v>375</v>
       </c>
       <c r="C2" s="38" t="n">
         <v>2002</v>
       </c>
       <c r="D2" s="24" t="s">
-        <v>794</v>
+        <v>849</v>
       </c>
       <c r="E2" s="24" t="s">
-        <v>795</v>
+        <v>850</v>
       </c>
       <c r="F2" s="24" t="s">
-        <v>796</v>
+        <v>851</v>
       </c>
       <c r="G2" s="24" t="s">
-        <v>797</v>
+        <v>852</v>
       </c>
       <c r="H2" s="24" t="s">
-        <v>798</v>
+        <v>853</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="24" t="s">
-        <v>799</v>
+        <v>854</v>
       </c>
       <c r="B3" s="24" t="s">
         <v>59</v>
@@ -9169,50 +9782,50 @@
         <v>2006</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>800</v>
+        <v>855</v>
       </c>
       <c r="E3" s="24" t="s">
-        <v>801</v>
+        <v>856</v>
       </c>
       <c r="F3" s="24" t="s">
-        <v>802</v>
+        <v>857</v>
       </c>
       <c r="G3" s="24" t="s">
-        <v>803</v>
+        <v>858</v>
       </c>
       <c r="H3" s="24" t="s">
-        <v>804</v>
+        <v>859</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="24" t="s">
-        <v>368</v>
+        <v>390</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>244</v>
+        <v>266</v>
       </c>
       <c r="C4" s="38" t="n">
         <v>1988</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>805</v>
+        <v>860</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>806</v>
+        <v>861</v>
       </c>
       <c r="F4" s="24" t="s">
-        <v>807</v>
+        <v>862</v>
       </c>
       <c r="G4" s="24" t="s">
-        <v>808</v>
+        <v>863</v>
       </c>
       <c r="H4" s="24" t="s">
-        <v>809</v>
+        <v>864</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="24" t="s">
-        <v>376</v>
+        <v>398</v>
       </c>
       <c r="B5" s="24" t="s">
         <v>92</v>
@@ -9221,204 +9834,204 @@
         <v>2001</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>261</v>
+        <v>283</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>810</v>
+        <v>865</v>
       </c>
       <c r="F5" s="24" t="s">
-        <v>654</v>
+        <v>709</v>
       </c>
       <c r="G5" s="24" t="s">
-        <v>811</v>
+        <v>866</v>
       </c>
       <c r="H5" s="24" t="s">
-        <v>812</v>
+        <v>867</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="24" t="s">
-        <v>381</v>
+        <v>403</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>382</v>
+        <v>404</v>
       </c>
       <c r="C6" s="38" t="n">
         <v>1995</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>261</v>
+        <v>283</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>813</v>
+        <v>868</v>
       </c>
       <c r="F6" s="24" t="s">
-        <v>654</v>
+        <v>709</v>
       </c>
       <c r="G6" s="24" t="s">
-        <v>814</v>
+        <v>869</v>
       </c>
       <c r="H6" s="24" t="s">
-        <v>386</v>
+        <v>408</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="24" t="s">
-        <v>815</v>
+        <v>870</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>816</v>
+        <v>871</v>
       </c>
       <c r="C7" s="38" t="n">
         <v>1990</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>817</v>
+        <v>872</v>
       </c>
       <c r="E7" s="24" t="s">
-        <v>818</v>
+        <v>873</v>
       </c>
       <c r="F7" s="24" t="s">
-        <v>819</v>
+        <v>874</v>
       </c>
       <c r="G7" s="24" t="s">
-        <v>820</v>
+        <v>875</v>
       </c>
       <c r="H7" s="24" t="s">
-        <v>821</v>
+        <v>876</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="24" t="s">
-        <v>822</v>
+        <v>877</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>316</v>
+        <v>338</v>
       </c>
       <c r="C8" s="38" t="n">
         <v>2001</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>261</v>
+        <v>283</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>695</v>
+        <v>750</v>
       </c>
       <c r="F8" s="24" t="s">
-        <v>823</v>
+        <v>878</v>
       </c>
       <c r="G8" s="24" t="s">
-        <v>824</v>
+        <v>879</v>
       </c>
       <c r="H8" s="24" t="s">
-        <v>825</v>
+        <v>880</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="24" t="s">
-        <v>826</v>
+        <v>881</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>353</v>
+        <v>375</v>
       </c>
       <c r="C9" s="38" t="n">
         <v>2003</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>827</v>
+        <v>882</v>
       </c>
       <c r="E9" s="24" t="s">
-        <v>828</v>
+        <v>883</v>
       </c>
       <c r="F9" s="24" t="s">
-        <v>829</v>
+        <v>884</v>
       </c>
       <c r="G9" s="24" t="s">
-        <v>830</v>
+        <v>885</v>
       </c>
       <c r="H9" s="24" t="s">
-        <v>831</v>
+        <v>886</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="24" t="s">
-        <v>832</v>
+        <v>887</v>
       </c>
       <c r="B10" s="24" t="s">
         <v>59</v>
       </c>
       <c r="C10" s="24"/>
       <c r="D10" s="24" t="s">
-        <v>833</v>
+        <v>888</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>834</v>
+        <v>889</v>
       </c>
       <c r="F10" s="24" t="s">
-        <v>835</v>
+        <v>890</v>
       </c>
       <c r="G10" s="24" t="s">
-        <v>836</v>
+        <v>891</v>
       </c>
       <c r="H10" s="24" t="s">
-        <v>837</v>
+        <v>892</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="24" t="s">
-        <v>329</v>
+        <v>351</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>838</v>
+        <v>893</v>
       </c>
       <c r="C11" s="38" t="n">
         <v>2007</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>839</v>
+        <v>894</v>
       </c>
       <c r="E11" s="24" t="s">
-        <v>840</v>
+        <v>895</v>
       </c>
       <c r="F11" s="24" t="s">
-        <v>841</v>
+        <v>896</v>
       </c>
       <c r="G11" s="24" t="s">
-        <v>842</v>
+        <v>897</v>
       </c>
       <c r="H11" s="24" t="s">
-        <v>843</v>
+        <v>898</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="24" t="s">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>844</v>
+        <v>899</v>
       </c>
       <c r="C12" s="38" t="n">
         <v>2001</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>845</v>
+        <v>900</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>846</v>
+        <v>901</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>847</v>
+        <v>902</v>
       </c>
       <c r="G12" s="24" t="s">
-        <v>848</v>
+        <v>903</v>
       </c>
       <c r="H12" s="24" t="s">
-        <v>849</v>
+        <v>904</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="24" t="s">
-        <v>850</v>
+        <v>905</v>
       </c>
       <c r="B13" s="24" t="s">
         <v>59</v>
@@ -9428,128 +10041,154 @@
       </c>
       <c r="D13" s="24"/>
       <c r="E13" s="24" t="s">
-        <v>851</v>
+        <v>906</v>
       </c>
       <c r="F13" s="24" t="s">
-        <v>852</v>
+        <v>907</v>
       </c>
       <c r="G13" s="24" t="s">
-        <v>853</v>
+        <v>908</v>
       </c>
       <c r="H13" s="24" t="s">
-        <v>854</v>
+        <v>909</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="24" t="s">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="C14" s="38" t="n">
         <v>1996</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>855</v>
+        <v>910</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>856</v>
+        <v>911</v>
       </c>
       <c r="F14" s="24" t="s">
-        <v>654</v>
+        <v>709</v>
       </c>
       <c r="G14" s="24" t="s">
-        <v>857</v>
+        <v>912</v>
       </c>
       <c r="H14" s="24" t="s">
-        <v>858</v>
+        <v>913</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="24" t="s">
-        <v>321</v>
+        <v>343</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>859</v>
+        <v>914</v>
       </c>
       <c r="C15" s="38" t="n">
         <v>1999</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>860</v>
+        <v>915</v>
       </c>
       <c r="E15" s="24" t="s">
-        <v>728</v>
+        <v>783</v>
       </c>
       <c r="F15" s="24" t="s">
-        <v>861</v>
+        <v>916</v>
       </c>
       <c r="G15" s="24" t="s">
-        <v>862</v>
+        <v>917</v>
       </c>
       <c r="H15" s="24" t="s">
-        <v>863</v>
+        <v>918</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="24" t="s">
-        <v>864</v>
+        <v>919</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>865</v>
+        <v>920</v>
       </c>
       <c r="C16" s="38" t="n">
         <v>1990</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>866</v>
+        <v>921</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>867</v>
+        <v>922</v>
       </c>
       <c r="F16" s="24" t="s">
-        <v>868</v>
+        <v>923</v>
       </c>
       <c r="G16" s="24" t="s">
-        <v>869</v>
+        <v>924</v>
       </c>
       <c r="H16" s="24" t="s">
-        <v>870</v>
+        <v>925</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="24" t="s">
-        <v>871</v>
+        <v>926</v>
       </c>
       <c r="B17" s="24" t="s">
         <v>59</v>
       </c>
       <c r="C17" s="24"/>
       <c r="D17" s="24" t="s">
-        <v>261</v>
+        <v>283</v>
       </c>
       <c r="E17" s="24" t="s">
-        <v>872</v>
+        <v>927</v>
       </c>
       <c r="F17" s="24" t="s">
-        <v>873</v>
+        <v>928</v>
       </c>
       <c r="G17" s="24" t="s">
-        <v>874</v>
+        <v>929</v>
       </c>
       <c r="H17" s="24" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="30" t="s">
-        <v>876</v>
+        <v>930</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="24" t="s">
+        <v>931</v>
+      </c>
+      <c r="B18" s="24" t="s">
+        <v>932</v>
+      </c>
+      <c r="C18" s="38" t="n">
+        <v>2003</v>
+      </c>
+      <c r="D18" s="24" t="s">
+        <v>933</v>
+      </c>
+      <c r="E18" s="24" t="s">
+        <v>934</v>
+      </c>
+      <c r="F18" s="24" t="s">
+        <v>935</v>
+      </c>
+      <c r="G18" s="24" t="s">
+        <v>936</v>
+      </c>
+      <c r="H18" s="24" t="s">
+        <v>937</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="31" t="s">
-        <v>877</v>
+      <c r="A20" s="30" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="31" t="s">
+        <v>939</v>
       </c>
     </row>
   </sheetData>
@@ -9568,7 +10207,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="54"/>
@@ -9581,197 +10220,285 @@
         <v>1</v>
       </c>
       <c r="B1" s="37" t="s">
-        <v>878</v>
+        <v>940</v>
       </c>
       <c r="C1" s="37" t="s">
-        <v>879</v>
+        <v>941</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="24" t="s">
-        <v>880</v>
+        <v>942</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>881</v>
+        <v>943</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>882</v>
+        <v>944</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="24" t="s">
-        <v>883</v>
+        <v>945</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>884</v>
+        <v>946</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>885</v>
+        <v>947</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="24" t="s">
-        <v>886</v>
+        <v>948</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>887</v>
+        <v>949</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>888</v>
+        <v>950</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="24" t="s">
-        <v>192</v>
+        <v>215</v>
       </c>
       <c r="B5" s="24" t="s">
         <v>92</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>889</v>
+        <v>951</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="24" t="s">
-        <v>890</v>
+        <v>952</v>
       </c>
       <c r="B6" s="24" t="s">
         <v>92</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>891</v>
+        <v>953</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="24" t="s">
-        <v>892</v>
+        <v>954</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>893</v>
+        <v>955</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>894</v>
+        <v>956</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="24" t="s">
-        <v>895</v>
+        <v>957</v>
       </c>
       <c r="B8" s="24" t="s">
         <v>92</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>896</v>
+        <v>958</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="24" t="s">
-        <v>897</v>
+        <v>959</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>898</v>
+        <v>960</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>899</v>
+        <v>961</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="24" t="s">
-        <v>900</v>
+        <v>962</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>901</v>
+        <v>963</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>902</v>
+        <v>964</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="24" t="s">
-        <v>903</v>
+        <v>965</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>904</v>
+        <v>966</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>905</v>
+        <v>967</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="24" t="s">
-        <v>906</v>
+        <v>968</v>
       </c>
       <c r="B12" s="24" t="s">
         <v>92</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>907</v>
+        <v>969</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="24" t="s">
-        <v>908</v>
+        <v>970</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>909</v>
+        <v>971</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>910</v>
+        <v>972</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="24" t="s">
-        <v>282</v>
+        <v>304</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>911</v>
+        <v>973</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>912</v>
+        <v>974</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="24" t="s">
-        <v>913</v>
+        <v>975</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>914</v>
+        <v>976</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>915</v>
+        <v>977</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="24" t="s">
-        <v>916</v>
+        <v>978</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>917</v>
+        <v>979</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>918</v>
+        <v>980</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="24" t="s">
-        <v>919</v>
+        <v>981</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>920</v>
+        <v>982</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>921</v>
+        <v>983</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="24" t="s">
-        <v>922</v>
+        <v>984</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>923</v>
+        <v>985</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>924</v>
+        <v>986</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="24" t="s">
+        <v>987</v>
+      </c>
+      <c r="B19" s="24" t="s">
+        <v>988</v>
+      </c>
+      <c r="C19" s="24" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="24" t="s">
+        <v>990</v>
+      </c>
+      <c r="B20" s="24" t="s">
+        <v>991</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="24" t="s">
+        <v>993</v>
+      </c>
+      <c r="B21" s="24" t="s">
+        <v>994</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="24" t="s">
+        <v>996</v>
+      </c>
+      <c r="B22" s="24" t="s">
+        <v>997</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="24" t="s">
+        <v>999</v>
+      </c>
+      <c r="B23" s="24" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="24" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B24" s="24" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="24" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B25" s="24" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="24" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B26" s="24" t="s">
+        <v>932</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>1009</v>
       </c>
     </row>
   </sheetData>
@@ -9799,12 +10526,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="39" t="s">
-        <v>925</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="40" t="s">
-        <v>926</v>
+        <v>1011</v>
       </c>
       <c r="B2" s="41" t="n">
         <v>2026</v>
@@ -9812,7 +10539,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="40" t="s">
-        <v>927</v>
+        <v>1012</v>
       </c>
       <c r="B3" s="42" t="n">
         <v>150000</v>
@@ -9820,7 +10547,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="40" t="s">
-        <v>928</v>
+        <v>1013</v>
       </c>
       <c r="B4" s="42" t="n">
         <v>200000</v>
@@ -9828,12 +10555,12 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="40" t="s">
-        <v>929</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="40" t="s">
-        <v>930</v>
+        <v>1015</v>
       </c>
       <c r="B6" s="43" t="n">
         <v>0.15</v>
@@ -9841,7 +10568,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="40" t="s">
-        <v>931</v>
+        <v>1016</v>
       </c>
       <c r="B7" s="44" t="n">
         <v>4</v>
@@ -9849,7 +10576,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="40" t="s">
-        <v>932</v>
+        <v>1017</v>
       </c>
       <c r="B8" s="44" t="n">
         <v>7</v>
@@ -9857,7 +10584,7 @@
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="40" t="s">
-        <v>933</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9865,32 +10592,32 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="39" t="s">
-        <v>934</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="40" t="s">
-        <v>935</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="40" t="s">
-        <v>936</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="40" t="s">
-        <v>937</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="40" t="s">
-        <v>938</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="40" t="s">
-        <v>939</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9898,42 +10625,42 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="39" t="s">
-        <v>940</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="40" t="s">
-        <v>941</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="40" t="s">
-        <v>942</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="40" t="s">
-        <v>943</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="40" t="s">
-        <v>944</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="40" t="s">
-        <v>945</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="40" t="s">
-        <v>946</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="40" t="s">
-        <v>947</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9941,37 +10668,37 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="39" t="s">
-        <v>948</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="40" t="s">
-        <v>949</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="40" t="s">
-        <v>950</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="40" t="s">
-        <v>951</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="40" t="s">
-        <v>952</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="40" t="s">
-        <v>953</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="40" t="s">
-        <v>954</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9979,22 +10706,22 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="39" t="s">
-        <v>955</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="40" t="s">
-        <v>956</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="40" t="s">
-        <v>957</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="40" t="s">
-        <v>958</v>
+        <v>1043</v>
       </c>
     </row>
   </sheetData>
